--- a/assets/LadenburgConsensuStatements.xlsx
+++ b/assets/LadenburgConsensuStatements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mspitschan/Projects/LadenburgConsensusStatements/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1A86B6-749A-A242-A218-22E042E258AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1478FA-EF4D-9F43-88B0-F0DA08DA0C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="880" windowWidth="17540" windowHeight="22500" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11880" yWindow="2680" windowWidth="25380" windowHeight="21660" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="4" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="1481">
   <si>
     <t>Number</t>
   </si>
@@ -7254,46 +7254,37 @@
     <t>Artemide</t>
   </si>
   <si>
-    <t>Leiden University Medical Center</t>
-  </si>
-  <si>
-    <t>Chrono@Work &amp; University of Groningen</t>
-  </si>
-  <si>
-    <t>National Research Council of Canada</t>
-  </si>
-  <si>
-    <t>Stanford University</t>
-  </si>
-  <si>
-    <t>Renske</t>
-  </si>
-  <si>
-    <t>Lok</t>
-  </si>
-  <si>
-    <t>Gordijn</t>
-  </si>
-  <si>
-    <t>Jennifer A.</t>
-  </si>
-  <si>
-    <t>Veitch</t>
-  </si>
-  <si>
-    <t>rlok@stanford.edu</t>
-  </si>
-  <si>
-    <t>Jennifer.Veitch@nrc-cnrc.gc.ca</t>
-  </si>
-  <si>
-    <t>L.Kervezee@lumc.nl</t>
-  </si>
-  <si>
-    <t>0000-0003-3183-4537</t>
-  </si>
-  <si>
-    <t>0000-0003-1684-5625</t>
+    <t>Kaynaklar</t>
+  </si>
+  <si>
+    <t>Referências</t>
+  </si>
+  <si>
+    <t>Bibliografia</t>
+  </si>
+  <si>
+    <t>참고문헌</t>
+  </si>
+  <si>
+    <t>Riferimenti</t>
+  </si>
+  <si>
+    <t>Références</t>
+  </si>
+  <si>
+    <t>参考文献 </t>
+  </si>
+  <si>
+    <t>Referenties</t>
+  </si>
+  <si>
+    <t>منابع</t>
+  </si>
+  <si>
+    <t>Referencer</t>
+  </si>
+  <si>
+    <t>Seznam literatury</t>
   </si>
 </sst>
 </file>
@@ -8447,7 +8438,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="44">
+  <cellStyleXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -8494,8 +8485,9 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8831,6 +8823,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="44"/>
     <xf numFmtId="0" fontId="31" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8846,51 +8839,52 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="44">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" xr:uid="{B2D74732-8E41-314C-B68A-0975ED16242F}"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+  <cellStyles count="45">
+    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="44" xr:uid="{B2D74732-8E41-314C-B68A-0975ED16242F}"/>
+    <cellStyle name="Link" xfId="42" builtinId="8"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="43" xr:uid="{70AE8D79-DF60-5941-BC6B-2804C19A889C}"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8906,9 +8900,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8946,7 +8940,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -9052,7 +9046,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -9711,7 +9705,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="119">
+    <row r="26" spans="1:6" ht="136">
       <c r="A26" t="s">
         <v>206</v>
       </c>
@@ -9758,7 +9752,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A6E799-3425-7049-AD78-3DEC34B23389}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="24" customWidth="1"/>
@@ -9766,7 +9760,7 @@
     <col min="3" max="5" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16">
+    <row r="1" spans="1:6" ht="16">
       <c r="A1" t="s">
         <v>1051</v>
       </c>
@@ -9782,8 +9776,11 @@
       <c r="E1" t="s">
         <v>1054</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="93" customHeight="1">
+      <c r="F1" s="108" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="93" customHeight="1">
       <c r="A2" s="116" t="s">
         <v>202</v>
       </c>
@@ -9800,7 +9797,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="85">
+    <row r="3" spans="1:6" ht="85">
       <c r="A3" s="116" t="s">
         <v>202</v>
       </c>
@@ -9817,7 +9814,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="136">
+    <row r="4" spans="1:6" ht="153">
       <c r="A4" s="116" t="s">
         <v>202</v>
       </c>
@@ -9834,7 +9831,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="117.75" customHeight="1">
+    <row r="5" spans="1:6" ht="117.75" customHeight="1">
       <c r="A5" s="116" t="s">
         <v>202</v>
       </c>
@@ -9851,7 +9848,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="150" customHeight="1">
+    <row r="6" spans="1:6" ht="150" customHeight="1">
       <c r="A6" s="116" t="s">
         <v>202</v>
       </c>
@@ -9868,7 +9865,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="68">
+    <row r="7" spans="1:6" ht="68">
       <c r="A7" s="116" t="s">
         <v>202</v>
       </c>
@@ -9885,7 +9882,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="91.5" customHeight="1">
+    <row r="8" spans="1:6" ht="91.5" customHeight="1">
       <c r="A8" s="116" t="s">
         <v>203</v>
       </c>
@@ -9902,7 +9899,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="102">
+    <row r="9" spans="1:6" ht="102">
       <c r="A9" s="116" t="s">
         <v>203</v>
       </c>
@@ -9919,7 +9916,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="51">
+    <row r="10" spans="1:6" ht="51">
       <c r="A10" s="116" t="s">
         <v>203</v>
       </c>
@@ -9936,7 +9933,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="68">
+    <row r="11" spans="1:6" ht="68">
       <c r="A11" s="116" t="s">
         <v>204</v>
       </c>
@@ -9953,7 +9950,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="102">
+    <row r="12" spans="1:6" ht="102">
       <c r="A12" s="116" t="s">
         <v>204</v>
       </c>
@@ -9970,7 +9967,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="68">
+    <row r="13" spans="1:6" ht="68">
       <c r="A13" s="116" t="s">
         <v>204</v>
       </c>
@@ -9987,7 +9984,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="68">
+    <row r="14" spans="1:6" ht="68">
       <c r="A14" s="116" t="s">
         <v>204</v>
       </c>
@@ -10004,7 +10001,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="85">
+    <row r="15" spans="1:6" ht="85">
       <c r="A15" s="116" t="s">
         <v>204</v>
       </c>
@@ -10021,7 +10018,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="68">
+    <row r="16" spans="1:6" ht="68">
       <c r="A16" s="116" t="s">
         <v>204</v>
       </c>
@@ -10123,7 +10120,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="51">
+    <row r="22" spans="1:5" ht="68">
       <c r="A22" s="116" t="s">
         <v>205</v>
       </c>
@@ -10257,6 +10254,9 @@
       <c r="E1" t="s">
         <v>1049</v>
       </c>
+      <c r="F1" s="108" t="s">
+        <v>1478</v>
+      </c>
     </row>
     <row r="2" spans="1:21" ht="111" customHeight="1">
       <c r="A2" s="72" t="s">
@@ -13643,17 +13643,17 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5344526-0759-5748-9599-6774FD0E2E70}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="65.1640625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="134.5" customWidth="1"/>
     <col min="4" max="4" width="42.33203125" customWidth="1"/>
-    <col min="5" max="5" width="55" style="132" customWidth="1"/>
+    <col min="5" max="5" width="55" style="133" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>199</v>
       </c>
@@ -13669,446 +13669,449 @@
       <c r="E1" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="34" customFormat="1" ht="19">
-      <c r="A2" s="135" t="s">
+      <c r="F1" s="108" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="19">
+      <c r="A2" s="136" t="s">
         <v>1356</v>
       </c>
       <c r="B2" s="33">
         <v>1</v>
       </c>
-      <c r="C2" s="133" t="s">
+      <c r="C2" s="134" t="s">
         <v>1371</v>
       </c>
-      <c r="D2" s="133" t="s">
+      <c r="D2" s="134" t="s">
         <v>1370</v>
       </c>
-      <c r="E2" s="133" t="s">
+      <c r="E2" s="134" t="s">
         <v>1369</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19">
-      <c r="A3" s="135" t="s">
+    <row r="3" spans="1:6" ht="19">
+      <c r="A3" s="136" t="s">
         <v>1356</v>
       </c>
       <c r="B3" s="33">
         <v>2</v>
       </c>
-      <c r="C3" s="136" t="s">
+      <c r="C3" s="137" t="s">
         <v>1368</v>
       </c>
-      <c r="D3" s="133" t="s">
+      <c r="D3" s="134" t="s">
         <v>1367</v>
       </c>
-      <c r="E3" s="133" t="s">
+      <c r="E3" s="134" t="s">
         <v>1366</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19">
-      <c r="A4" s="135" t="s">
+    <row r="4" spans="1:6" ht="19">
+      <c r="A4" s="136" t="s">
         <v>1356</v>
       </c>
       <c r="B4" s="33">
         <v>3</v>
       </c>
-      <c r="C4" s="134" t="s">
+      <c r="C4" s="135" t="s">
         <v>1365</v>
       </c>
-      <c r="D4" s="133" t="s">
+      <c r="D4" s="134" t="s">
         <v>1364</v>
       </c>
-      <c r="E4" s="133" t="s">
+      <c r="E4" s="134" t="s">
         <v>1363</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19">
-      <c r="A5" s="135" t="s">
+    <row r="5" spans="1:6" ht="19">
+      <c r="A5" s="136" t="s">
         <v>1356</v>
       </c>
       <c r="B5" s="31">
         <v>4</v>
       </c>
-      <c r="C5" s="134" t="s">
+      <c r="C5" s="135" t="s">
         <v>1362</v>
       </c>
-      <c r="D5" s="133" t="s">
+      <c r="D5" s="134" t="s">
         <v>1361</v>
       </c>
-      <c r="E5" s="133" t="s">
+      <c r="E5" s="134" t="s">
         <v>1360</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="19">
-      <c r="A6" s="135" t="s">
+    <row r="6" spans="1:6" ht="19">
+      <c r="A6" s="136" t="s">
         <v>1356</v>
       </c>
       <c r="B6" s="31">
         <v>5</v>
       </c>
-      <c r="C6" s="134" t="s">
+      <c r="C6" s="135" t="s">
         <v>1359</v>
       </c>
-      <c r="D6" s="133" t="s">
+      <c r="D6" s="134" t="s">
         <v>1358</v>
       </c>
-      <c r="E6" s="133" t="s">
+      <c r="E6" s="134" t="s">
         <v>1357</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19">
-      <c r="A7" s="135" t="s">
+    <row r="7" spans="1:6" ht="19">
+      <c r="A7" s="136" t="s">
         <v>1356</v>
       </c>
       <c r="B7" s="31">
         <v>6</v>
       </c>
-      <c r="C7" s="134" t="s">
+      <c r="C7" s="135" t="s">
         <v>1355</v>
       </c>
-      <c r="D7" s="133" t="s">
+      <c r="D7" s="134" t="s">
         <v>1354</v>
       </c>
-      <c r="E7" s="133" t="s">
+      <c r="E7" s="134" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19">
-      <c r="A8" s="135" t="s">
+    <row r="8" spans="1:6" ht="19">
+      <c r="A8" s="136" t="s">
         <v>1347</v>
       </c>
       <c r="B8" s="31">
         <v>7</v>
       </c>
-      <c r="C8" s="134" t="s">
+      <c r="C8" s="135" t="s">
         <v>1352</v>
       </c>
-      <c r="D8" s="133" t="s">
+      <c r="D8" s="134" t="s">
         <v>1351</v>
       </c>
-      <c r="E8" s="133" t="s">
+      <c r="E8" s="134" t="s">
         <v>1350</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="19">
-      <c r="A9" s="135" t="s">
+    <row r="9" spans="1:6" ht="19">
+      <c r="A9" s="136" t="s">
         <v>1347</v>
       </c>
       <c r="B9" s="31">
         <v>8</v>
       </c>
-      <c r="C9" s="134" t="s">
+      <c r="C9" s="135" t="s">
         <v>1349</v>
       </c>
-      <c r="D9" s="133" t="s">
+      <c r="D9" s="134" t="s">
         <v>1349</v>
       </c>
-      <c r="E9" s="133" t="s">
+      <c r="E9" s="134" t="s">
         <v>1348</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="19">
-      <c r="A10" s="135" t="s">
+    <row r="10" spans="1:6" ht="19">
+      <c r="A10" s="136" t="s">
         <v>1347</v>
       </c>
       <c r="B10" s="31">
         <v>9</v>
       </c>
-      <c r="C10" s="134" t="s">
+      <c r="C10" s="135" t="s">
         <v>1346</v>
       </c>
-      <c r="D10" s="133" t="s">
+      <c r="D10" s="134" t="s">
         <v>1346</v>
       </c>
-      <c r="E10" s="133" t="s">
+      <c r="E10" s="134" t="s">
         <v>1345</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="19">
-      <c r="A11" s="135" t="s">
+    <row r="11" spans="1:6" ht="19">
+      <c r="A11" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B11" s="31">
         <v>10</v>
       </c>
-      <c r="C11" s="134" t="s">
+      <c r="C11" s="135" t="s">
         <v>1344</v>
       </c>
-      <c r="D11" s="133" t="s">
+      <c r="D11" s="134" t="s">
         <v>1343</v>
       </c>
-      <c r="E11" s="133" t="s">
+      <c r="E11" s="134" t="s">
         <v>1342</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="135" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B12" s="31">
         <v>11</v>
       </c>
-      <c r="C12" s="134" t="s">
+      <c r="C12" s="135" t="s">
         <v>1341</v>
       </c>
-      <c r="D12" s="133" t="s">
+      <c r="D12" s="134" t="s">
         <v>1340</v>
       </c>
-      <c r="E12" s="133" t="s">
+      <c r="E12" s="134" t="s">
         <v>1339</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="19">
-      <c r="A13" s="135" t="s">
+    <row r="13" spans="1:6" ht="19">
+      <c r="A13" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B13" s="31">
         <v>12</v>
       </c>
-      <c r="C13" s="134" t="s">
+      <c r="C13" s="135" t="s">
         <v>1338</v>
       </c>
-      <c r="D13" s="133" t="s">
+      <c r="D13" s="134" t="s">
         <v>1337</v>
       </c>
-      <c r="E13" s="133" t="s">
+      <c r="E13" s="134" t="s">
         <v>1336</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20">
-      <c r="A14" s="135" t="s">
+    <row r="14" spans="1:6" ht="20">
+      <c r="A14" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B14" s="31">
         <v>13</v>
       </c>
-      <c r="C14" s="134" t="s">
+      <c r="C14" s="135" t="s">
         <v>1335</v>
       </c>
-      <c r="D14" s="133" t="s">
+      <c r="D14" s="134" t="s">
         <v>1334</v>
       </c>
-      <c r="E14" s="133" t="s">
+      <c r="E14" s="134" t="s">
         <v>1333</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="135" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B15" s="31">
         <v>14</v>
       </c>
-      <c r="C15" s="134" t="s">
+      <c r="C15" s="135" t="s">
         <v>1332</v>
       </c>
-      <c r="D15" s="133" t="s">
+      <c r="D15" s="134" t="s">
         <v>1331</v>
       </c>
-      <c r="E15" s="133" t="s">
+      <c r="E15" s="134" t="s">
         <v>1330</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="19">
-      <c r="A16" s="135" t="s">
+    <row r="16" spans="1:6" ht="19">
+      <c r="A16" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B16" s="31">
         <v>15</v>
       </c>
-      <c r="C16" s="134" t="s">
+      <c r="C16" s="135" t="s">
         <v>1329</v>
       </c>
-      <c r="D16" s="133" t="s">
+      <c r="D16" s="134" t="s">
         <v>1328</v>
       </c>
-      <c r="E16" s="133" t="s">
+      <c r="E16" s="134" t="s">
         <v>1328</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="135" t="s">
+      <c r="A17" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B17" s="31">
         <v>16</v>
       </c>
-      <c r="C17" s="134" t="s">
+      <c r="C17" s="135" t="s">
         <v>1327</v>
       </c>
-      <c r="D17" s="133" t="s">
+      <c r="D17" s="134" t="s">
         <v>1326</v>
       </c>
-      <c r="E17" s="133" t="s">
+      <c r="E17" s="134" t="s">
         <v>1326</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="19">
-      <c r="A18" s="135" t="s">
+      <c r="A18" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B18" s="31">
         <v>17</v>
       </c>
-      <c r="C18" s="134" t="s">
+      <c r="C18" s="135" t="s">
         <v>1325</v>
       </c>
-      <c r="D18" s="133" t="s">
+      <c r="D18" s="134" t="s">
         <v>1324</v>
       </c>
-      <c r="E18" s="133" t="s">
+      <c r="E18" s="134" t="s">
         <v>1323</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="19">
-      <c r="A19" s="135" t="s">
+      <c r="A19" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B19" s="31">
         <v>18</v>
       </c>
-      <c r="C19" s="134" t="s">
+      <c r="C19" s="135" t="s">
         <v>1322</v>
       </c>
-      <c r="D19" s="133" t="s">
+      <c r="D19" s="134" t="s">
         <v>1321</v>
       </c>
-      <c r="E19" s="133" t="s">
+      <c r="E19" s="134" t="s">
         <v>1320</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="19">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B20" s="31">
         <v>19</v>
       </c>
-      <c r="C20" s="134" t="s">
+      <c r="C20" s="135" t="s">
         <v>1319</v>
       </c>
-      <c r="D20" s="133" t="s">
+      <c r="D20" s="134" t="s">
         <v>1318</v>
       </c>
-      <c r="E20" s="133" t="s">
+      <c r="E20" s="134" t="s">
         <v>1317</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="135" t="s">
+      <c r="A21" s="136" t="s">
         <v>1316</v>
       </c>
       <c r="B21" s="31">
         <v>20</v>
       </c>
-      <c r="C21" s="134" t="s">
+      <c r="C21" s="135" t="s">
         <v>1315</v>
       </c>
-      <c r="D21" s="133" t="s">
+      <c r="D21" s="134" t="s">
         <v>1314</v>
       </c>
-      <c r="E21" s="133" t="s">
+      <c r="E21" s="134" t="s">
         <v>1313</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="19">
-      <c r="A22" s="135" t="s">
+      <c r="A22" s="136" t="s">
         <v>1306</v>
       </c>
       <c r="B22" s="31">
         <v>21</v>
       </c>
-      <c r="C22" s="134" t="s">
+      <c r="C22" s="135" t="s">
         <v>1312</v>
       </c>
-      <c r="D22" s="133" t="s">
+      <c r="D22" s="134" t="s">
         <v>1311</v>
       </c>
-      <c r="E22" s="133" t="s">
+      <c r="E22" s="134" t="s">
         <v>1310</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="19">
-      <c r="A23" s="135" t="s">
+      <c r="A23" s="136" t="s">
         <v>1306</v>
       </c>
       <c r="B23" s="31">
         <v>22</v>
       </c>
-      <c r="C23" s="134" t="s">
+      <c r="C23" s="135" t="s">
         <v>1309</v>
       </c>
-      <c r="D23" s="133" t="s">
+      <c r="D23" s="134" t="s">
         <v>1308</v>
       </c>
-      <c r="E23" s="133" t="s">
+      <c r="E23" s="134" t="s">
         <v>1307</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="19">
-      <c r="A24" s="135" t="s">
+      <c r="A24" s="136" t="s">
         <v>1306</v>
       </c>
       <c r="B24" s="31">
         <v>23</v>
       </c>
-      <c r="C24" s="134" t="s">
+      <c r="C24" s="135" t="s">
         <v>1305</v>
       </c>
-      <c r="D24" s="133" t="s">
+      <c r="D24" s="134" t="s">
         <v>1304</v>
       </c>
-      <c r="E24" s="133" t="s">
+      <c r="E24" s="134" t="s">
         <v>1303</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="19">
-      <c r="A25" s="135" t="s">
+      <c r="A25" s="136" t="s">
         <v>1295</v>
       </c>
       <c r="B25" s="31">
         <v>24</v>
       </c>
-      <c r="C25" s="134" t="s">
+      <c r="C25" s="135" t="s">
         <v>1302</v>
       </c>
-      <c r="D25" s="133" t="s">
+      <c r="D25" s="134" t="s">
         <v>1301</v>
       </c>
-      <c r="E25" s="133" t="s">
+      <c r="E25" s="134" t="s">
         <v>1300</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="19">
-      <c r="A26" s="135" t="s">
+      <c r="A26" s="136" t="s">
         <v>1299</v>
       </c>
       <c r="B26" s="31">
         <v>25</v>
       </c>
-      <c r="C26" s="134" t="s">
+      <c r="C26" s="135" t="s">
         <v>1298</v>
       </c>
-      <c r="D26" s="133" t="s">
+      <c r="D26" s="134" t="s">
         <v>1297</v>
       </c>
-      <c r="E26" s="133" t="s">
+      <c r="E26" s="134" t="s">
         <v>1296</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20" thickBot="1">
-      <c r="A27" s="135" t="s">
+      <c r="A27" s="136" t="s">
         <v>1295</v>
       </c>
       <c r="B27" s="28">
         <v>26</v>
       </c>
-      <c r="C27" s="134" t="s">
+      <c r="C27" s="135" t="s">
         <v>1294</v>
       </c>
-      <c r="D27" s="133" t="s">
+      <c r="D27" s="134" t="s">
         <v>1293</v>
       </c>
-      <c r="E27" s="133" t="s">
+      <c r="E27" s="134" t="s">
         <v>1292</v>
       </c>
     </row>
@@ -14119,16 +14122,16 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD20F301-A307-714C-9879-0F7D8927DA0D}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25.1640625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="42.33203125" customWidth="1"/>
-    <col min="5" max="5" width="42.33203125" style="132" customWidth="1"/>
+    <col min="5" max="5" width="42.33203125" style="133" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1060</v>
       </c>
@@ -14144,8 +14147,11 @@
       <c r="E1" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="34" customFormat="1" ht="68">
+      <c r="F1" s="108" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="68">
       <c r="A2" s="23" t="s">
         <v>1453</v>
       </c>
@@ -14162,7 +14168,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="68">
+    <row r="3" spans="1:6" ht="68">
       <c r="A3" s="23" t="s">
         <v>1453</v>
       </c>
@@ -14179,7 +14185,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="102">
+    <row r="4" spans="1:6" ht="102">
       <c r="A4" s="23" t="s">
         <v>1453</v>
       </c>
@@ -14196,7 +14202,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="102">
+    <row r="5" spans="1:6" ht="102">
       <c r="A5" s="23" t="s">
         <v>1453</v>
       </c>
@@ -14213,7 +14219,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="102">
+    <row r="6" spans="1:6" ht="102">
       <c r="A6" s="23" t="s">
         <v>1453</v>
       </c>
@@ -14230,7 +14236,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="57">
+    <row r="7" spans="1:6" ht="57">
       <c r="A7" s="23" t="s">
         <v>1453</v>
       </c>
@@ -14247,7 +14253,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="68">
+    <row r="8" spans="1:6" ht="68">
       <c r="A8" s="23" t="s">
         <v>1443</v>
       </c>
@@ -14264,7 +14270,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="85">
+    <row r="9" spans="1:6" ht="85">
       <c r="A9" s="23" t="s">
         <v>1443</v>
       </c>
@@ -14281,7 +14287,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="38">
+    <row r="10" spans="1:6" ht="38">
       <c r="A10" s="23" t="s">
         <v>1443</v>
       </c>
@@ -14298,7 +14304,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51">
+    <row r="11" spans="1:6" ht="51">
       <c r="A11" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14315,7 +14321,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="85">
+    <row r="12" spans="1:6" ht="85">
       <c r="A12" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14332,7 +14338,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="57">
+    <row r="13" spans="1:6" ht="57">
       <c r="A13" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14349,7 +14355,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="57">
+    <row r="14" spans="1:6" ht="57">
       <c r="A14" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14366,7 +14372,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="76">
+    <row r="15" spans="1:6" ht="76">
       <c r="A15" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14383,7 +14389,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="51">
+    <row r="16" spans="1:6" ht="51">
       <c r="A16" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14400,7 +14406,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="51">
+    <row r="17" spans="1:5" ht="68">
       <c r="A17" s="23" t="s">
         <v>1409</v>
       </c>
@@ -14485,7 +14491,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="51">
+    <row r="22" spans="1:5" ht="57">
       <c r="A22" s="23" t="s">
         <v>1399</v>
       </c>
@@ -14678,7 +14684,7 @@
       <c r="K2" s="72" t="s">
         <v>1178</v>
       </c>
-      <c r="L2" s="131" t="s">
+      <c r="L2" s="132" t="s">
         <v>1287</v>
       </c>
       <c r="M2" s="23" t="s">
@@ -14719,7 +14725,7 @@
       <c r="K3" s="72" t="s">
         <v>1179</v>
       </c>
-      <c r="L3" s="131" t="s">
+      <c r="L3" s="132" t="s">
         <v>1288</v>
       </c>
       <c r="M3" s="23" t="s">
@@ -14760,7 +14766,7 @@
       <c r="K4" s="72" t="s">
         <v>1180</v>
       </c>
-      <c r="L4" s="131" t="s">
+      <c r="L4" s="132" t="s">
         <v>1289</v>
       </c>
       <c r="M4" s="23" t="s">
@@ -14801,7 +14807,7 @@
       <c r="K5" s="72" t="s">
         <v>1181</v>
       </c>
-      <c r="L5" s="131" t="s">
+      <c r="L5" s="132" t="s">
         <v>1290</v>
       </c>
       <c r="M5" s="23" t="s">
@@ -14842,7 +14848,7 @@
       <c r="K6" s="72" t="s">
         <v>1182</v>
       </c>
-      <c r="L6" s="131" t="s">
+      <c r="L6" s="132" t="s">
         <v>1291</v>
       </c>
       <c r="M6" s="23" t="s">
@@ -14856,7 +14862,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D128F0C-3C92-B24F-9D24-BF419F807E89}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
@@ -14891,10 +14897,10 @@
         <v>160</v>
       </c>
       <c r="B2" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>588</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>587</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>428</v>
@@ -14909,803 +14915,803 @@
         <v>590</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="34">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>428</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1470</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>1069</v>
+        <v>302</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>447</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>448</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>428</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>449</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>450</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>451</v>
+        <v>302</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>1476</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>428</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1471</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>1094</v>
+        <v>302</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>428</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1472</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>1482</v>
+        <v>302</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>1474</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>428</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1473</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>1483</v>
+        <v>337</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>424</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>308</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>309</v>
+        <v>337</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>427</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>315</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>435</v>
+      </c>
+      <c r="G9" s="38"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>302</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>320</v>
+        <v>214</v>
+      </c>
+      <c r="B10" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D10" t="s">
+        <v>799</v>
+      </c>
+      <c r="E10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F10" t="s">
+        <v>439</v>
+      </c>
+      <c r="G10" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>325</v>
+        <v>214</v>
+      </c>
+      <c r="B11" t="s">
+        <v>441</v>
+      </c>
+      <c r="C11" t="s">
+        <v>442</v>
+      </c>
+      <c r="D11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E11" t="s">
+        <v>444</v>
+      </c>
+      <c r="F11" t="s">
+        <v>445</v>
+      </c>
+      <c r="G11" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>421</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>422</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>423</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>425</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>798</v>
+        <v>214</v>
+      </c>
+      <c r="B12" t="s">
+        <v>447</v>
+      </c>
+      <c r="C12" t="s">
+        <v>448</v>
+      </c>
+      <c r="D12" t="s">
+        <v>428</v>
+      </c>
+      <c r="E12" t="s">
+        <v>449</v>
+      </c>
+      <c r="F12" t="s">
+        <v>450</v>
+      </c>
+      <c r="G12" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>426</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>428</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>429</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>430</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>797</v>
+        <v>214</v>
+      </c>
+      <c r="B13" t="s">
+        <v>452</v>
+      </c>
+      <c r="C13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13" t="s">
+        <v>454</v>
+      </c>
+      <c r="E13" t="s">
+        <v>455</v>
+      </c>
+      <c r="F13" t="s">
+        <v>456</v>
+      </c>
+      <c r="G13" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>337</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>431</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>432</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>433</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>434</v>
-      </c>
-      <c r="F14" s="35" t="s">
-        <v>435</v>
-      </c>
-      <c r="G14" s="38"/>
+        <v>214</v>
+      </c>
+      <c r="B14" t="s">
+        <v>458</v>
+      </c>
+      <c r="C14" t="s">
+        <v>459</v>
+      </c>
+      <c r="D14" t="s">
+        <v>460</v>
+      </c>
+      <c r="E14" t="s">
+        <v>461</v>
+      </c>
+      <c r="F14" t="s">
+        <v>462</v>
+      </c>
+      <c r="G14" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="C15" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="D15" t="s">
-        <v>799</v>
+        <v>466</v>
       </c>
       <c r="E15" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="F15" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="G15" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" t="s">
-        <v>441</v>
-      </c>
-      <c r="C16" t="s">
-        <v>442</v>
-      </c>
-      <c r="D16" t="s">
-        <v>443</v>
-      </c>
-      <c r="E16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F16" t="s">
-        <v>445</v>
-      </c>
-      <c r="G16" t="s">
-        <v>446</v>
+        <v>554</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>562</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>564</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>555</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B17" t="s">
-        <v>447</v>
-      </c>
-      <c r="C17" t="s">
-        <v>448</v>
-      </c>
-      <c r="D17" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" t="s">
-        <v>449</v>
-      </c>
-      <c r="F17" t="s">
-        <v>450</v>
-      </c>
-      <c r="G17" t="s">
-        <v>451</v>
+        <v>554</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>565</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>566</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>567</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>558</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" t="s">
-        <v>452</v>
-      </c>
-      <c r="C18" t="s">
-        <v>453</v>
-      </c>
-      <c r="D18" t="s">
-        <v>454</v>
-      </c>
-      <c r="E18" t="s">
-        <v>455</v>
-      </c>
-      <c r="F18" t="s">
-        <v>456</v>
-      </c>
-      <c r="G18" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>554</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>568</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>569</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>567</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>560</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>556</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18">
       <c r="A19" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" t="s">
-        <v>458</v>
-      </c>
-      <c r="C19" t="s">
-        <v>459</v>
-      </c>
-      <c r="D19" t="s">
-        <v>460</v>
-      </c>
-      <c r="E19" t="s">
-        <v>461</v>
-      </c>
-      <c r="F19" t="s">
-        <v>462</v>
-      </c>
-      <c r="G19" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>586</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>570</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>571</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>573</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18">
       <c r="A20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B20" t="s">
-        <v>464</v>
-      </c>
-      <c r="C20" t="s">
-        <v>465</v>
-      </c>
-      <c r="D20" t="s">
-        <v>466</v>
-      </c>
-      <c r="E20" t="s">
-        <v>467</v>
-      </c>
-      <c r="F20" t="s">
-        <v>468</v>
-      </c>
-      <c r="G20" t="s">
-        <v>469</v>
+        <v>586</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>574</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>575</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>576</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>577</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>562</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>563</v>
-      </c>
-      <c r="D21" s="47" t="s">
-        <v>564</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>555</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>578</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>579</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>580</v>
+      </c>
+      <c r="F21" s="49" t="s">
+        <v>581</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="23">
       <c r="A22" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>565</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>566</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>567</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>558</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="G22" s="48" t="s">
-        <v>559</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>582</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>583</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>584</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>585</v>
+      </c>
+      <c r="G22" s="51"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>554</v>
-      </c>
-      <c r="B23" s="49" t="s">
-        <v>568</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>569</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>567</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>560</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>556</v>
-      </c>
-      <c r="G23" s="47" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="18">
+        <v>775</v>
+      </c>
+      <c r="B23" s="80" t="s">
+        <v>776</v>
+      </c>
+      <c r="C23" s="80" t="s">
+        <v>777</v>
+      </c>
+      <c r="D23" s="80" t="s">
+        <v>778</v>
+      </c>
+      <c r="E23" s="80" t="s">
+        <v>779</v>
+      </c>
+      <c r="F23" s="80" t="s">
+        <v>780</v>
+      </c>
+      <c r="G23" s="88" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>586</v>
-      </c>
-      <c r="B24" s="49" t="s">
-        <v>570</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>571</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>306</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="F24" s="49" t="s">
-        <v>573</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18">
+        <v>775</v>
+      </c>
+      <c r="B24" s="80" t="s">
+        <v>781</v>
+      </c>
+      <c r="C24" s="80" t="s">
+        <v>782</v>
+      </c>
+      <c r="D24" s="80" t="s">
+        <v>318</v>
+      </c>
+      <c r="E24" s="82" t="s">
+        <v>783</v>
+      </c>
+      <c r="F24" s="83" t="s">
+        <v>784</v>
+      </c>
+      <c r="G24" s="89" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>586</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>574</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>575</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>306</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>576</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>577</v>
-      </c>
-      <c r="G25" s="46" t="s">
-        <v>592</v>
+        <v>775</v>
+      </c>
+      <c r="B25" s="80" t="s">
+        <v>785</v>
+      </c>
+      <c r="C25" s="80" t="s">
+        <v>786</v>
+      </c>
+      <c r="D25" s="80" t="s">
+        <v>778</v>
+      </c>
+      <c r="E25" s="81" t="s">
+        <v>787</v>
+      </c>
+      <c r="F25" s="80" t="s">
+        <v>788</v>
+      </c>
+      <c r="G25" s="84" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>586</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>578</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>579</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>306</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>580</v>
-      </c>
-      <c r="F26" s="49" t="s">
-        <v>581</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="23">
+        <v>775</v>
+      </c>
+      <c r="B26" s="85" t="s">
+        <v>789</v>
+      </c>
+      <c r="C26" s="80" t="s">
+        <v>790</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="E26" s="86" t="s">
+        <v>791</v>
+      </c>
+      <c r="F26" s="87" t="s">
+        <v>792</v>
+      </c>
+      <c r="G26" s="81" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>586</v>
+        <v>816</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>578</v>
+        <v>800</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>582</v>
+        <v>801</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>583</v>
+        <v>802</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>584</v>
+        <v>803</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>585</v>
-      </c>
-      <c r="G27" s="51"/>
+        <v>804</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>775</v>
-      </c>
-      <c r="B28" s="80" t="s">
-        <v>776</v>
-      </c>
-      <c r="C28" s="80" t="s">
-        <v>777</v>
-      </c>
-      <c r="D28" s="80" t="s">
-        <v>778</v>
-      </c>
-      <c r="E28" s="80" t="s">
-        <v>779</v>
-      </c>
-      <c r="F28" s="80" t="s">
-        <v>780</v>
-      </c>
-      <c r="G28" s="88" t="s">
-        <v>793</v>
+        <v>816</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>806</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>807</v>
+      </c>
+      <c r="D28" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>808</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>809</v>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>775</v>
-      </c>
-      <c r="B29" s="80" t="s">
-        <v>781</v>
-      </c>
-      <c r="C29" s="80" t="s">
-        <v>782</v>
-      </c>
-      <c r="D29" s="80" t="s">
-        <v>318</v>
-      </c>
-      <c r="E29" s="82" t="s">
-        <v>783</v>
-      </c>
-      <c r="F29" s="83" t="s">
-        <v>784</v>
-      </c>
-      <c r="G29" s="89" t="s">
-        <v>794</v>
+        <v>816</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>811</v>
+      </c>
+      <c r="C29" s="49" t="s">
+        <v>812</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>813</v>
+      </c>
+      <c r="F29" s="49" t="s">
+        <v>814</v>
+      </c>
+      <c r="G29" s="49" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>775</v>
-      </c>
-      <c r="B30" s="80" t="s">
-        <v>785</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>786</v>
-      </c>
-      <c r="D30" s="80" t="s">
-        <v>778</v>
-      </c>
-      <c r="E30" s="81" t="s">
-        <v>787</v>
-      </c>
-      <c r="F30" s="80" t="s">
-        <v>788</v>
-      </c>
-      <c r="G30" s="84" t="s">
-        <v>795</v>
+        <v>993</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>994</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>995</v>
+      </c>
+      <c r="D30" s="49" t="s">
+        <v>996</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>997</v>
+      </c>
+      <c r="F30" s="49" t="s">
+        <v>998</v>
+      </c>
+      <c r="G30" s="49" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>775</v>
-      </c>
-      <c r="B31" s="85" t="s">
-        <v>789</v>
-      </c>
-      <c r="C31" s="80" t="s">
-        <v>790</v>
-      </c>
-      <c r="D31" s="24" t="s">
+        <v>993</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D31" s="49" t="s">
         <v>428</v>
       </c>
-      <c r="E31" s="86" t="s">
-        <v>791</v>
-      </c>
-      <c r="F31" s="87" t="s">
-        <v>792</v>
-      </c>
-      <c r="G31" s="81" t="s">
-        <v>796</v>
-      </c>
+      <c r="E31" s="46" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G31" s="46"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>816</v>
+        <v>993</v>
       </c>
       <c r="B32" s="49" t="s">
-        <v>800</v>
+        <v>1004</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>801</v>
+        <v>1005</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>802</v>
+        <v>428</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>803</v>
+        <v>1006</v>
       </c>
       <c r="F32" s="49" t="s">
-        <v>804</v>
-      </c>
-      <c r="G32" s="46" t="s">
-        <v>805</v>
+        <v>1003</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>816</v>
-      </c>
-      <c r="B33" s="49" t="s">
-        <v>806</v>
-      </c>
-      <c r="C33" s="49" t="s">
-        <v>807</v>
-      </c>
-      <c r="D33" s="49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="E33" s="46" t="s">
-        <v>808</v>
-      </c>
-      <c r="F33" s="49" t="s">
-        <v>809</v>
-      </c>
-      <c r="G33" s="46" t="s">
-        <v>810</v>
+      <c r="E33" s="109" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>1069</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>816</v>
-      </c>
-      <c r="B34" s="49" t="s">
-        <v>811</v>
-      </c>
-      <c r="C34" s="49" t="s">
-        <v>812</v>
-      </c>
-      <c r="D34" s="49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="E34" s="46" t="s">
-        <v>813</v>
-      </c>
-      <c r="F34" s="49" t="s">
-        <v>814</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>815</v>
+      <c r="E34" s="109" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>993</v>
-      </c>
-      <c r="B35" s="49" t="s">
-        <v>994</v>
-      </c>
-      <c r="C35" s="49" t="s">
-        <v>995</v>
-      </c>
-      <c r="D35" s="49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D35" s="24" t="s">
         <v>996</v>
       </c>
-      <c r="E35" s="46" t="s">
-        <v>997</v>
-      </c>
-      <c r="F35" s="49" t="s">
-        <v>998</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>999</v>
+      <c r="E35" s="109" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>993</v>
-      </c>
-      <c r="B36" s="49" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C36" s="49" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>428</v>
-      </c>
-      <c r="E36" s="46" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G36" s="46"/>
+        <v>1050</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E36" s="109" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>1084</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>993</v>
-      </c>
-      <c r="B37" s="49" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D37" s="49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D37" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="E37" s="46" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>1007</v>
+      <c r="E37" s="109" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F37" s="85" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G37" s="109" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -15713,319 +15719,199 @@
         <v>1050</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>1066</v>
+        <v>1090</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="E38" s="109" t="s">
-        <v>1067</v>
+      <c r="E38" s="110" t="s">
+        <v>1091</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>1069</v>
+        <v>1092</v>
+      </c>
+      <c r="G38" s="109" t="s">
+        <v>1094</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D39" s="24" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B39" s="49" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C39" s="49" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D39" s="49" t="s">
         <v>428</v>
       </c>
-      <c r="E39" s="109" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F39" s="24" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>1074</v>
+      <c r="E39" s="120" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F39" s="49" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G39" s="121" t="s">
+        <v>1188</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D40" s="24" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B40" s="49" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C40" s="49" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D40" s="49" t="s">
         <v>996</v>
       </c>
-      <c r="E40" s="109" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G40" s="24" t="s">
-        <v>1078</v>
+      <c r="E40" s="122" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F40" s="49" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G40" s="123" t="s">
+        <v>1193</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E41" s="109" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G41" s="24" t="s">
-        <v>1084</v>
+        <v>1055</v>
+      </c>
+      <c r="B41" s="130" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C41" s="130" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D41" s="130" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E41" s="131" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F41" s="130" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G41" s="131" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="E42" s="109" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F42" s="85" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G42" s="109" t="s">
-        <v>1093</v>
-      </c>
+        <v>1055</v>
+      </c>
+      <c r="B42" s="130" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C42" s="130" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D42" s="130"/>
+      <c r="E42" s="131" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F42" s="130" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G42" s="130"/>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D43" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="E43" s="110" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G43" s="109" t="s">
-        <v>1094</v>
-      </c>
+        <v>1059</v>
+      </c>
+      <c r="B43" s="49" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D43" s="49"/>
+      <c r="E43" s="46" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G43" s="46"/>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>1183</v>
+        <v>1059</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>1184</v>
+        <v>1380</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>1185</v>
+        <v>1381</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>428</v>
-      </c>
-      <c r="E44" s="120" t="s">
-        <v>1186</v>
+        <v>1382</v>
+      </c>
+      <c r="E44" s="46" t="s">
+        <v>1383</v>
       </c>
       <c r="F44" s="49" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G44" s="121" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B45" s="49" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C45" s="49" t="s">
-        <v>1190</v>
-      </c>
-      <c r="D45" s="49" t="s">
-        <v>996</v>
-      </c>
-      <c r="E45" s="122" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F45" s="49" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G45" s="123" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B46" s="130" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C46" s="130" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D46" s="130" t="s">
-        <v>1279</v>
-      </c>
-      <c r="E46" s="46" t="s">
-        <v>1280</v>
-      </c>
-      <c r="F46" s="130" t="s">
-        <v>1281</v>
-      </c>
-      <c r="G46" s="46" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B47" s="130" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C47" s="130" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D47" s="130"/>
-      <c r="E47" s="46" t="s">
-        <v>1284</v>
-      </c>
-      <c r="F47" s="130" t="s">
-        <v>1285</v>
-      </c>
-      <c r="G47" s="130"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B48" s="49" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C48" s="49" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D48" s="49"/>
-      <c r="E48" s="46" t="s">
-        <v>1379</v>
-      </c>
-      <c r="F48" s="49" t="s">
-        <v>1469</v>
-      </c>
-      <c r="G48" s="46"/>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B49" s="49" t="s">
-        <v>1380</v>
-      </c>
-      <c r="C49" s="49" t="s">
-        <v>1381</v>
-      </c>
-      <c r="D49" s="49" t="s">
-        <v>1382</v>
-      </c>
-      <c r="E49" s="46" t="s">
-        <v>1383</v>
-      </c>
-      <c r="F49" s="49" t="s">
         <v>1384</v>
       </c>
-      <c r="G49" s="46" t="s">
+      <c r="G44" s="46" t="s">
         <v>1385</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E9" r:id="rId1" xr:uid="{E3CFFE38-E6D6-714C-8CB2-6C7908765724}"/>
-    <hyperlink ref="E10" r:id="rId2" xr:uid="{F2E60514-AAF2-A440-AE6A-F3B7A800911F}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{B079DF0E-018E-9341-8C9C-61E8233F15E0}"/>
-    <hyperlink ref="E11" r:id="rId4" xr:uid="{1AC7D81A-6207-0940-9797-1B54146D29C9}"/>
-    <hyperlink ref="G13" r:id="rId5" display="https://orcid.org/0000-0001-6769-1983" xr:uid="{C44E8F08-6368-D74F-B1B2-A27AC4441576}"/>
-    <hyperlink ref="G12" r:id="rId6" display="https://orcid.org/0000-0003-2477-6869" xr:uid="{0489100D-EEF4-B949-AEFF-A6A4DC402620}"/>
-    <hyperlink ref="E21" r:id="rId7" xr:uid="{5F4E651F-562B-E24E-9CD1-9B3C1936C245}"/>
-    <hyperlink ref="E23" r:id="rId8" xr:uid="{F1125717-1141-4D42-A3A9-699125D01684}"/>
-    <hyperlink ref="E22" r:id="rId9" xr:uid="{1F332E72-AFB1-6744-B32C-C21F6FEBAA6E}"/>
-    <hyperlink ref="G21" r:id="rId10" display="https://orcid.org/0000-0002-1381-253X" xr:uid="{8EAB4384-125C-1B4B-BE58-8509C671817B}"/>
-    <hyperlink ref="E24" r:id="rId11" xr:uid="{87A5E650-E56F-F44A-8B6D-3500B47533C8}"/>
-    <hyperlink ref="E25" r:id="rId12" xr:uid="{BD2ECD0E-F5A3-804E-99C9-70ABA0785192}"/>
-    <hyperlink ref="G24" r:id="rId13" display="https://orcid.org/0000-0003-0951-780X" xr:uid="{DDA7CB87-9DEF-444A-B5E5-4DA5387FEAE7}"/>
-    <hyperlink ref="G25" r:id="rId14" display="https://orcid.org/0009-0007-7565-9714" xr:uid="{C3278E97-D66C-C04F-A534-F2DCF73A26A5}"/>
-    <hyperlink ref="E27" r:id="rId15" xr:uid="{A72A8784-3E65-CD4A-9CEA-D6821E18F4F0}"/>
-    <hyperlink ref="G26" r:id="rId16" display="https://orcid.org/0000-0003-4348-3690" xr:uid="{E9AFF3C1-A433-7741-A54F-44C2C489E5C4}"/>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{E3CFFE38-E6D6-714C-8CB2-6C7908765724}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{F2E60514-AAF2-A440-AE6A-F3B7A800911F}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{B079DF0E-018E-9341-8C9C-61E8233F15E0}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{1AC7D81A-6207-0940-9797-1B54146D29C9}"/>
+    <hyperlink ref="G8" r:id="rId5" display="https://orcid.org/0000-0001-6769-1983" xr:uid="{C44E8F08-6368-D74F-B1B2-A27AC4441576}"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://orcid.org/0000-0003-2477-6869" xr:uid="{0489100D-EEF4-B949-AEFF-A6A4DC402620}"/>
+    <hyperlink ref="E16" r:id="rId7" xr:uid="{5F4E651F-562B-E24E-9CD1-9B3C1936C245}"/>
+    <hyperlink ref="E18" r:id="rId8" xr:uid="{F1125717-1141-4D42-A3A9-699125D01684}"/>
+    <hyperlink ref="E17" r:id="rId9" xr:uid="{1F332E72-AFB1-6744-B32C-C21F6FEBAA6E}"/>
+    <hyperlink ref="G16" r:id="rId10" display="https://orcid.org/0000-0002-1381-253X" xr:uid="{8EAB4384-125C-1B4B-BE58-8509C671817B}"/>
+    <hyperlink ref="E19" r:id="rId11" xr:uid="{87A5E650-E56F-F44A-8B6D-3500B47533C8}"/>
+    <hyperlink ref="E20" r:id="rId12" xr:uid="{BD2ECD0E-F5A3-804E-99C9-70ABA0785192}"/>
+    <hyperlink ref="G19" r:id="rId13" display="https://orcid.org/0000-0003-0951-780X" xr:uid="{DDA7CB87-9DEF-444A-B5E5-4DA5387FEAE7}"/>
+    <hyperlink ref="G20" r:id="rId14" display="https://orcid.org/0009-0007-7565-9714" xr:uid="{C3278E97-D66C-C04F-A534-F2DCF73A26A5}"/>
+    <hyperlink ref="E22" r:id="rId15" xr:uid="{A72A8784-3E65-CD4A-9CEA-D6821E18F4F0}"/>
+    <hyperlink ref="G21" r:id="rId16" display="https://orcid.org/0000-0003-4348-3690" xr:uid="{E9AFF3C1-A433-7741-A54F-44C2C489E5C4}"/>
     <hyperlink ref="E2" r:id="rId17" xr:uid="{632BF422-FA2D-144A-9443-DEA9263E44B9}"/>
-    <hyperlink ref="G28" r:id="rId18" display="https://orcid.org/0000-0002-8726-306X" xr:uid="{84D128EF-A321-C14C-9A6C-47FF211C7B25}"/>
-    <hyperlink ref="E29" r:id="rId19" xr:uid="{CAB810DD-1FD3-D84E-B12A-6B1D1E12C04D}"/>
-    <hyperlink ref="G29" r:id="rId20" display="http://orcid.org/0000-0003-3535-7635" xr:uid="{E4794437-B59F-DB4C-B151-F9DDAECC9286}"/>
-    <hyperlink ref="E30" r:id="rId21" xr:uid="{E1B39D4A-FBDF-AB42-AFEC-5C4DBDFAE8A7}"/>
-    <hyperlink ref="G30" r:id="rId22" display="https://orcid.org/0000-0001-7604-0189" xr:uid="{4339A64C-035B-6245-919A-A8374AC5693D}"/>
-    <hyperlink ref="G31" r:id="rId23" display="https://orcid.org/0000-0001-7055-4701" xr:uid="{767A7D54-6548-E84D-981B-2EBD5369EDFF}"/>
-    <hyperlink ref="E32" r:id="rId24" xr:uid="{5E51343F-FF89-F14E-9FE3-8814A36D3C70}"/>
-    <hyperlink ref="E34" r:id="rId25" xr:uid="{A027007D-B16C-2D4A-A8C6-EE858E3A1D33}"/>
-    <hyperlink ref="E33" r:id="rId26" xr:uid="{DC6269BB-3246-D949-BC02-C59C24825789}"/>
-    <hyperlink ref="E35" r:id="rId27" xr:uid="{F9219FC4-650D-A647-94A8-FBD0AA56CFB7}"/>
-    <hyperlink ref="E36" r:id="rId28" xr:uid="{53118788-31F1-0149-8A20-F71DC03A8C9E}"/>
-    <hyperlink ref="E37" r:id="rId29" xr:uid="{6674C05C-673B-944F-98AB-75A0E6DAD5D7}"/>
-    <hyperlink ref="E38" r:id="rId30" xr:uid="{1E6CE376-85BC-EA4A-910D-DE1116AE6626}"/>
-    <hyperlink ref="E39" r:id="rId31" xr:uid="{8EE7483F-11FE-1248-B139-1CACB6186AA8}"/>
-    <hyperlink ref="E40" r:id="rId32" xr:uid="{77795DE8-0FC2-7341-81B6-278D1A2C4C8C}"/>
-    <hyperlink ref="E41" r:id="rId33" display="mailto:manon.de.deyne@vub.be" xr:uid="{AA5027B5-300A-F74C-B55B-E65732A75CDC}"/>
-    <hyperlink ref="E42" r:id="rId34" xr:uid="{C7E7CDCA-035E-1E4D-8532-EBEF677A2F25}"/>
-    <hyperlink ref="G42" r:id="rId35" display="https://orcid.org/0000-0002-1370-2090" xr:uid="{03A1AF0E-1F44-4940-A09A-56AB0017FB99}"/>
-    <hyperlink ref="E43" r:id="rId36" xr:uid="{1B1D269B-6E40-9748-A5C1-2D0CBA515977}"/>
-    <hyperlink ref="G43" r:id="rId37" display="https://orcid.org/0000-0001-9521-8085" xr:uid="{E54A6775-6C19-3A4B-BB48-482DD27FEE2E}"/>
-    <hyperlink ref="E44" r:id="rId38" xr:uid="{10759E79-85C3-DE40-8D6A-6C833FE92CB4}"/>
-    <hyperlink ref="G46" r:id="rId39" display="https://orcid.org/0000-0002-4202-4655" xr:uid="{848147C0-A9CA-E642-883A-ABE0683BC099}"/>
-    <hyperlink ref="E46" r:id="rId40" xr:uid="{1F029844-97BD-AA4C-B9EC-4978EC0229B0}"/>
-    <hyperlink ref="E47" r:id="rId41" xr:uid="{48E273F6-ED98-9A4D-B926-3360708B7FC2}"/>
-    <hyperlink ref="E48" r:id="rId42" xr:uid="{AF1B887C-35B7-8E4D-91D8-29E3CA5ACE86}"/>
-    <hyperlink ref="E49" r:id="rId43" xr:uid="{D9F36DA3-D0B7-7E42-85A4-528353BCA0E2}"/>
-    <hyperlink ref="E7" r:id="rId44" xr:uid="{40ED56F6-B773-AE47-ADE5-D486624FA922}"/>
-    <hyperlink ref="E6" r:id="rId45" xr:uid="{BFBCA679-676B-2142-9CF7-90BEE47AEF3C}"/>
-    <hyperlink ref="E5" r:id="rId46" xr:uid="{E288DD64-BDB2-F34C-8BDF-186D74BFA64F}"/>
-    <hyperlink ref="E3" r:id="rId47" xr:uid="{2D45CCE2-CA40-9942-AE5E-A35107A86068}"/>
-    <hyperlink ref="E4" r:id="rId48" xr:uid="{0DE5FBF5-CA34-7D4F-8638-16D4532F099F}"/>
+    <hyperlink ref="G23" r:id="rId18" display="https://orcid.org/0000-0002-8726-306X" xr:uid="{84D128EF-A321-C14C-9A6C-47FF211C7B25}"/>
+    <hyperlink ref="E24" r:id="rId19" xr:uid="{CAB810DD-1FD3-D84E-B12A-6B1D1E12C04D}"/>
+    <hyperlink ref="G24" r:id="rId20" display="http://orcid.org/0000-0003-3535-7635" xr:uid="{E4794437-B59F-DB4C-B151-F9DDAECC9286}"/>
+    <hyperlink ref="E25" r:id="rId21" xr:uid="{E1B39D4A-FBDF-AB42-AFEC-5C4DBDFAE8A7}"/>
+    <hyperlink ref="G25" r:id="rId22" display="https://orcid.org/0000-0001-7604-0189" xr:uid="{4339A64C-035B-6245-919A-A8374AC5693D}"/>
+    <hyperlink ref="G26" r:id="rId23" display="https://orcid.org/0000-0001-7055-4701" xr:uid="{767A7D54-6548-E84D-981B-2EBD5369EDFF}"/>
+    <hyperlink ref="E27" r:id="rId24" xr:uid="{5E51343F-FF89-F14E-9FE3-8814A36D3C70}"/>
+    <hyperlink ref="E29" r:id="rId25" xr:uid="{A027007D-B16C-2D4A-A8C6-EE858E3A1D33}"/>
+    <hyperlink ref="E28" r:id="rId26" xr:uid="{DC6269BB-3246-D949-BC02-C59C24825789}"/>
+    <hyperlink ref="E30" r:id="rId27" xr:uid="{F9219FC4-650D-A647-94A8-FBD0AA56CFB7}"/>
+    <hyperlink ref="E31" r:id="rId28" xr:uid="{53118788-31F1-0149-8A20-F71DC03A8C9E}"/>
+    <hyperlink ref="E32" r:id="rId29" xr:uid="{6674C05C-673B-944F-98AB-75A0E6DAD5D7}"/>
+    <hyperlink ref="E33" r:id="rId30" xr:uid="{1E6CE376-85BC-EA4A-910D-DE1116AE6626}"/>
+    <hyperlink ref="E34" r:id="rId31" xr:uid="{8EE7483F-11FE-1248-B139-1CACB6186AA8}"/>
+    <hyperlink ref="E35" r:id="rId32" xr:uid="{77795DE8-0FC2-7341-81B6-278D1A2C4C8C}"/>
+    <hyperlink ref="E36" r:id="rId33" display="mailto:manon.de.deyne@vub.be" xr:uid="{AA5027B5-300A-F74C-B55B-E65732A75CDC}"/>
+    <hyperlink ref="E37" r:id="rId34" xr:uid="{C7E7CDCA-035E-1E4D-8532-EBEF677A2F25}"/>
+    <hyperlink ref="G37" r:id="rId35" display="https://orcid.org/0000-0002-1370-2090" xr:uid="{03A1AF0E-1F44-4940-A09A-56AB0017FB99}"/>
+    <hyperlink ref="E38" r:id="rId36" xr:uid="{1B1D269B-6E40-9748-A5C1-2D0CBA515977}"/>
+    <hyperlink ref="G38" r:id="rId37" display="https://orcid.org/0000-0001-9521-8085" xr:uid="{E54A6775-6C19-3A4B-BB48-482DD27FEE2E}"/>
+    <hyperlink ref="E39" r:id="rId38" xr:uid="{10759E79-85C3-DE40-8D6A-6C833FE92CB4}"/>
+    <hyperlink ref="G41" r:id="rId39" display="https://orcid.org/0000-0002-4202-4655" xr:uid="{848147C0-A9CA-E642-883A-ABE0683BC099}"/>
+    <hyperlink ref="E41" r:id="rId40" xr:uid="{1F029844-97BD-AA4C-B9EC-4978EC0229B0}"/>
+    <hyperlink ref="E42" r:id="rId41" xr:uid="{48E273F6-ED98-9A4D-B926-3360708B7FC2}"/>
+    <hyperlink ref="E43" r:id="rId42" xr:uid="{AF1B887C-35B7-8E4D-91D8-29E3CA5ACE86}"/>
+    <hyperlink ref="E44" r:id="rId43" xr:uid="{D9F36DA3-D0B7-7E42-85A4-528353BCA0E2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16473,7 +16359,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="102">
+    <row r="11" spans="1:6" ht="119">
       <c r="A11" t="s">
         <v>209</v>
       </c>
@@ -16794,7 +16680,9 @@
       <c r="E1" t="s">
         <v>1012</v>
       </c>
-      <c r="F1"/>
+      <c r="F1" s="108" t="s">
+        <v>1470</v>
+      </c>
     </row>
     <row r="2" spans="1:6" ht="68">
       <c r="A2" s="12" t="s">
@@ -17246,7 +17134,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1870FBA-EDD6-F747-8146-AD8380227C7B}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="33.83203125" style="25" customWidth="1"/>
@@ -17255,7 +17143,7 @@
     <col min="5" max="5" width="45.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1013</v>
       </c>
@@ -17271,8 +17159,11 @@
       <c r="E1" t="s">
         <v>1017</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="34" customFormat="1" ht="102">
+      <c r="F1" s="108" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="119">
       <c r="A2" s="23" t="s">
         <v>405</v>
       </c>
@@ -17289,7 +17180,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="85">
+    <row r="3" spans="1:6" ht="85">
       <c r="A3" s="23" t="s">
         <v>405</v>
       </c>
@@ -17306,7 +17197,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="119">
+    <row r="4" spans="1:6" ht="119">
       <c r="A4" s="23" t="s">
         <v>405</v>
       </c>
@@ -17323,7 +17214,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="119">
+    <row r="5" spans="1:6" ht="119">
       <c r="A5" s="23" t="s">
         <v>405</v>
       </c>
@@ -17340,7 +17231,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="136">
+    <row r="6" spans="1:6" ht="136">
       <c r="A6" s="23" t="s">
         <v>405</v>
       </c>
@@ -17357,7 +17248,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="68">
+    <row r="7" spans="1:6" ht="68">
       <c r="A7" s="23" t="s">
         <v>405</v>
       </c>
@@ -17374,7 +17265,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="78" customHeight="1">
+    <row r="8" spans="1:6" ht="78" customHeight="1">
       <c r="A8" s="23" t="s">
         <v>395</v>
       </c>
@@ -17391,7 +17282,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="85">
+    <row r="9" spans="1:6" ht="85">
       <c r="A9" s="23" t="s">
         <v>395</v>
       </c>
@@ -17408,7 +17299,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="51">
+    <row r="10" spans="1:6" ht="51">
       <c r="A10" s="23" t="s">
         <v>395</v>
       </c>
@@ -17425,7 +17316,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="68">
+    <row r="11" spans="1:6" ht="68">
       <c r="A11" s="23" t="s">
         <v>361</v>
       </c>
@@ -17442,7 +17333,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="102">
+    <row r="12" spans="1:6" ht="102">
       <c r="A12" s="23" t="s">
         <v>361</v>
       </c>
@@ -17459,7 +17350,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="68">
+    <row r="13" spans="1:6" ht="68">
       <c r="A13" s="23" t="s">
         <v>361</v>
       </c>
@@ -17476,7 +17367,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="51">
+    <row r="14" spans="1:6" ht="51">
       <c r="A14" s="23" t="s">
         <v>361</v>
       </c>
@@ -17493,7 +17384,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="85">
+    <row r="15" spans="1:6" ht="102">
       <c r="A15" s="23" t="s">
         <v>361</v>
       </c>
@@ -17510,7 +17401,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="51">
+    <row r="16" spans="1:6" ht="51">
       <c r="A16" s="23" t="s">
         <v>361</v>
       </c>
@@ -17721,7 +17612,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E08B14F-287D-9E4F-82CD-595A79363C01}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="49.6640625" customWidth="1"/>
@@ -17729,7 +17620,7 @@
     <col min="3" max="5" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1018</v>
       </c>
@@ -17745,8 +17636,11 @@
       <c r="E1" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="34" customFormat="1" ht="119">
+      <c r="F1" s="108" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="119">
       <c r="A2" s="41" t="s">
         <v>541</v>
       </c>
@@ -17763,7 +17657,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="170">
+    <row r="3" spans="1:6" ht="170">
       <c r="A3" s="41" t="s">
         <v>541</v>
       </c>
@@ -17780,7 +17674,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="221">
+    <row r="4" spans="1:6" ht="221">
       <c r="A4" s="41" t="s">
         <v>541</v>
       </c>
@@ -17797,7 +17691,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="102">
+    <row r="5" spans="1:6" ht="102">
       <c r="A5" s="41" t="s">
         <v>541</v>
       </c>
@@ -17814,7 +17708,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="153">
+    <row r="6" spans="1:6" ht="153">
       <c r="A6" s="41" t="s">
         <v>541</v>
       </c>
@@ -17831,7 +17725,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="102">
+    <row r="7" spans="1:6" ht="102">
       <c r="A7" s="41" t="s">
         <v>537</v>
       </c>
@@ -17848,7 +17742,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="119">
+    <row r="8" spans="1:6" ht="119">
       <c r="A8" s="41" t="s">
         <v>527</v>
       </c>
@@ -17865,7 +17759,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="102">
+    <row r="9" spans="1:6" ht="119">
       <c r="A9" s="41" t="s">
         <v>527</v>
       </c>
@@ -17882,7 +17776,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="85">
+    <row r="10" spans="1:6" ht="85">
       <c r="A10" s="41" t="s">
         <v>527</v>
       </c>
@@ -17899,7 +17793,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="68">
+    <row r="11" spans="1:6" ht="68">
       <c r="A11" s="41" t="s">
         <v>493</v>
       </c>
@@ -17916,7 +17810,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="102">
+    <row r="12" spans="1:6" ht="102">
       <c r="A12" s="41" t="s">
         <v>493</v>
       </c>
@@ -17933,7 +17827,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="68">
+    <row r="13" spans="1:6" ht="68">
       <c r="A13" s="41" t="s">
         <v>493</v>
       </c>
@@ -17950,7 +17844,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="68">
+    <row r="14" spans="1:6" ht="68">
       <c r="A14" s="41" t="s">
         <v>493</v>
       </c>
@@ -17967,7 +17861,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="102">
+    <row r="15" spans="1:6" ht="102">
       <c r="A15" s="41" t="s">
         <v>493</v>
       </c>
@@ -17984,7 +17878,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="68">
+    <row r="16" spans="1:6" ht="68">
       <c r="A16" s="41" t="s">
         <v>493</v>
       </c>
@@ -18195,7 +18089,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD1BAFA5-BB3F-3746-96CA-1E15CD5F496C}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.33203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="58" style="53" customWidth="1"/>
@@ -18204,7 +18098,7 @@
     <col min="6" max="16384" width="13.33203125" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1033</v>
       </c>
@@ -18220,8 +18114,11 @@
       <c r="E1" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="76">
+      <c r="F1" s="108" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="76">
       <c r="A2" s="57" t="s">
         <v>661</v>
       </c>
@@ -18238,7 +18135,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57">
+    <row r="3" spans="1:6" ht="57">
       <c r="A3" s="57" t="s">
         <v>661</v>
       </c>
@@ -18255,7 +18152,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="114">
+    <row r="4" spans="1:6" ht="114">
       <c r="A4" s="57" t="s">
         <v>661</v>
       </c>
@@ -18272,7 +18169,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="76">
+    <row r="5" spans="1:6" ht="76">
       <c r="A5" s="57" t="s">
         <v>661</v>
       </c>
@@ -18289,7 +18186,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="76">
+    <row r="6" spans="1:6" ht="76">
       <c r="A6" s="57" t="s">
         <v>661</v>
       </c>
@@ -18306,7 +18203,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="58.5" customHeight="1">
+    <row r="7" spans="1:6" ht="58.5" customHeight="1">
       <c r="A7" s="57" t="s">
         <v>661</v>
       </c>
@@ -18323,7 +18220,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="57">
+    <row r="8" spans="1:6" ht="57">
       <c r="A8" s="57" t="s">
         <v>651</v>
       </c>
@@ -18340,7 +18237,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="76">
+    <row r="9" spans="1:6" ht="76">
       <c r="A9" s="57" t="s">
         <v>651</v>
       </c>
@@ -18357,7 +18254,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="38">
+    <row r="10" spans="1:6" ht="38">
       <c r="A10" s="57" t="s">
         <v>651</v>
       </c>
@@ -18374,7 +18271,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="38">
+    <row r="11" spans="1:6" ht="38">
       <c r="A11" s="57" t="s">
         <v>617</v>
       </c>
@@ -18391,7 +18288,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="76">
+    <row r="12" spans="1:6" ht="76">
       <c r="A12" s="57" t="s">
         <v>617</v>
       </c>
@@ -18408,7 +18305,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="57">
+    <row r="13" spans="1:6" ht="57">
       <c r="A13" s="57" t="s">
         <v>617</v>
       </c>
@@ -18425,7 +18322,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="57">
+    <row r="14" spans="1:6" ht="57">
       <c r="A14" s="57" t="s">
         <v>617</v>
       </c>
@@ -18442,7 +18339,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="57">
+    <row r="15" spans="1:6" ht="57">
       <c r="A15" s="57" t="s">
         <v>617</v>
       </c>
@@ -18459,7 +18356,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="57">
+    <row r="16" spans="1:6" ht="57">
       <c r="A16" s="57" t="s">
         <v>617</v>
       </c>
@@ -18646,7 +18543,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="77" thickBot="1">
+    <row r="27" spans="1:5" ht="96" thickBot="1">
       <c r="A27" s="57" t="s">
         <v>597</v>
       </c>
@@ -18696,6 +18593,9 @@
       <c r="E1" t="s">
         <v>1027</v>
       </c>
+      <c r="F1" s="108" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="2" spans="1:22" ht="102">
       <c r="A2" s="72" t="s">
@@ -19164,7 +19064,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A873EFD-FDC9-F34B-9E47-4FB43415AA3A}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="49.6640625" customWidth="1"/>
@@ -19172,7 +19072,7 @@
     <col min="3" max="5" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1038</v>
       </c>
@@ -19188,8 +19088,11 @@
       <c r="E1" t="s">
         <v>1042</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="34" customFormat="1" ht="102">
+      <c r="F1" s="108" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="102">
       <c r="A2" s="23" t="s">
         <v>904</v>
       </c>
@@ -19206,7 +19109,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="85">
+    <row r="3" spans="1:6" ht="85">
       <c r="A3" s="23" t="s">
         <v>904</v>
       </c>
@@ -19223,7 +19126,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="119">
+    <row r="4" spans="1:6" ht="119">
       <c r="A4" s="23" t="s">
         <v>904</v>
       </c>
@@ -19240,7 +19143,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="136">
+    <row r="5" spans="1:6" ht="136">
       <c r="A5" s="23" t="s">
         <v>904</v>
       </c>
@@ -19257,7 +19160,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="136">
+    <row r="6" spans="1:6" ht="136">
       <c r="A6" s="23" t="s">
         <v>904</v>
       </c>
@@ -19274,7 +19177,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="95">
+    <row r="7" spans="1:6" ht="95">
       <c r="A7" s="23" t="s">
         <v>904</v>
       </c>
@@ -19291,7 +19194,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="102">
+    <row r="8" spans="1:6" ht="102">
       <c r="A8" s="23" t="s">
         <v>885</v>
       </c>
@@ -19308,7 +19211,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="85">
+    <row r="9" spans="1:6" ht="85">
       <c r="A9" s="23" t="s">
         <v>885</v>
       </c>
@@ -19325,7 +19228,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="57">
+    <row r="10" spans="1:6" ht="57">
       <c r="A10" s="23" t="s">
         <v>885</v>
       </c>
@@ -19342,7 +19245,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="85">
+    <row r="11" spans="1:6" ht="85">
       <c r="A11" s="23" t="s">
         <v>875</v>
       </c>
@@ -19359,7 +19262,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="119">
+    <row r="12" spans="1:6" ht="119">
       <c r="A12" s="23" t="s">
         <v>875</v>
       </c>
@@ -19376,7 +19279,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="76">
+    <row r="13" spans="1:6" ht="76">
       <c r="A13" s="23" t="s">
         <v>875</v>
       </c>
@@ -19393,7 +19296,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="76">
+    <row r="14" spans="1:6" ht="76">
       <c r="A14" s="23" t="s">
         <v>875</v>
       </c>
@@ -19410,7 +19313,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="85">
+    <row r="15" spans="1:6" ht="102">
       <c r="A15" s="23" t="s">
         <v>875</v>
       </c>
@@ -19427,7 +19330,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="68">
+    <row r="16" spans="1:6" ht="68">
       <c r="A16" s="23" t="s">
         <v>875</v>
       </c>
@@ -19495,7 +19398,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="68">
+    <row r="20" spans="1:5" ht="85">
       <c r="A20" s="23" t="s">
         <v>875</v>
       </c>
@@ -19512,7 +19415,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="95">
+    <row r="21" spans="1:5" ht="114">
       <c r="A21" s="23" t="s">
         <v>875</v>
       </c>
@@ -19597,7 +19500,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="119">
+    <row r="26" spans="1:5" ht="136">
       <c r="A26" s="23" t="s">
         <v>831</v>
       </c>
@@ -19638,7 +19541,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73049A3F-8369-7B4D-8239-B0CE97E178CB}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
@@ -19646,7 +19549,7 @@
     <col min="3" max="5" width="42.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1028</v>
       </c>
@@ -19662,8 +19565,11 @@
       <c r="E1" t="s">
         <v>1032</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="34" customFormat="1" ht="51">
+      <c r="F1" s="108" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="51">
       <c r="A2" s="23" t="s">
         <v>972</v>
       </c>
@@ -19680,7 +19586,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="68">
+    <row r="3" spans="1:6" ht="68">
       <c r="A3" s="23" t="s">
         <v>972</v>
       </c>
@@ -19697,7 +19603,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="68">
+    <row r="4" spans="1:6" ht="68">
       <c r="A4" s="23" t="s">
         <v>972</v>
       </c>
@@ -19714,7 +19620,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="85">
+    <row r="5" spans="1:6" ht="85">
       <c r="A5" s="23" t="s">
         <v>972</v>
       </c>
@@ -19731,7 +19637,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="68">
+    <row r="6" spans="1:6" ht="68">
       <c r="A6" s="23" t="s">
         <v>972</v>
       </c>
@@ -19748,7 +19654,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="34">
+    <row r="7" spans="1:6" ht="34">
       <c r="A7" s="23" t="s">
         <v>972</v>
       </c>
@@ -19765,7 +19671,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="68">
+    <row r="8" spans="1:6" ht="68">
       <c r="A8" s="23" t="s">
         <v>962</v>
       </c>
@@ -19782,7 +19688,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="68">
+    <row r="9" spans="1:6" ht="68">
       <c r="A9" s="23" t="s">
         <v>962</v>
       </c>
@@ -19799,7 +19705,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="34">
+    <row r="10" spans="1:6" ht="34">
       <c r="A10" s="23" t="s">
         <v>962</v>
       </c>
@@ -19816,7 +19722,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51">
+    <row r="11" spans="1:6" ht="51">
       <c r="A11" s="23" t="s">
         <v>928</v>
       </c>
@@ -19833,7 +19739,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="85">
+    <row r="12" spans="1:6" ht="85">
       <c r="A12" s="23" t="s">
         <v>928</v>
       </c>
@@ -19850,7 +19756,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="34">
+    <row r="13" spans="1:6" ht="34">
       <c r="A13" s="23" t="s">
         <v>928</v>
       </c>
@@ -19867,7 +19773,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="34">
+    <row r="14" spans="1:6" ht="34">
       <c r="A14" s="23" t="s">
         <v>928</v>
       </c>
@@ -19884,7 +19790,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="68">
+    <row r="15" spans="1:6" ht="68">
       <c r="A15" s="23" t="s">
         <v>928</v>
       </c>
@@ -19901,7 +19807,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="34">
+    <row r="16" spans="1:6" ht="34">
       <c r="A16" s="23" t="s">
         <v>928</v>
       </c>

--- a/assets/LadenburgConsensuStatements.xlsx
+++ b/assets/LadenburgConsensuStatements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1478FA-EF4D-9F43-88B0-F0DA08DA0C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E5AD0F-1B36-6349-954F-A503A8893933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11880" yWindow="2680" windowWidth="25380" windowHeight="21660" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12400" yWindow="620" windowWidth="35980" windowHeight="21980" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="4" r:id="rId1"/>
@@ -22,13 +22,15 @@
     <sheet name="Italian" sheetId="10" r:id="rId7"/>
     <sheet name="French" sheetId="11" r:id="rId8"/>
     <sheet name="Chinese" sheetId="12" r:id="rId9"/>
-    <sheet name="Dutch" sheetId="14" r:id="rId10"/>
-    <sheet name="Persian" sheetId="15" r:id="rId11"/>
-    <sheet name="Danish" sheetId="16" r:id="rId12"/>
-    <sheet name="Czech" sheetId="18" r:id="rId13"/>
-    <sheet name="Key Messages" sheetId="2" r:id="rId14"/>
-    <sheet name="Contributors" sheetId="6" r:id="rId15"/>
-    <sheet name="Phrasetable" sheetId="13" r:id="rId16"/>
+    <sheet name="Japanese" sheetId="19" r:id="rId10"/>
+    <sheet name="Spanish" sheetId="20" r:id="rId11"/>
+    <sheet name="Dutch" sheetId="14" r:id="rId12"/>
+    <sheet name="Persian" sheetId="15" r:id="rId13"/>
+    <sheet name="Danish" sheetId="16" r:id="rId14"/>
+    <sheet name="Czech" sheetId="18" r:id="rId15"/>
+    <sheet name="Key Messages" sheetId="2" r:id="rId16"/>
+    <sheet name="Contributors" sheetId="6" r:id="rId17"/>
+    <sheet name="Phrasetable" sheetId="13" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_Toc192690236" localSheetId="1">German!#REF!</definedName>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="1702">
   <si>
     <t>Number</t>
   </si>
@@ -7285,13 +7287,1715 @@
   </si>
   <si>
     <t>Seznam literatury</t>
+  </si>
+  <si>
+    <t>生体リズム、睡眠、覚醒、気分、健康に及ぼす光の影響に対する科学的、一般的関心が高まっている。技術と科学の進歩により、研究者はさまざまな波長や強度をより正確に研究できるようになっている。</t>
+  </si>
+  <si>
+    <t>科学者たちは、光が生体機能や健康全般にどのような影響を与えるかを探求し続けている。</t>
+    <rPh sb="9" eb="11">
+      <t>ｾｲﾀｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の生理学的影響は、現在活発に研究されている分野である。</t>
+    <rPh sb="6" eb="8">
+      <t>ｴｲｷｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の非視覚的作用に関する研究（24-26）</t>
+    <rPh sb="0" eb="1">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="2" eb="8">
+      <t>ﾋｼｶｸﾃｷｻﾖｳ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ｶﾝ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ｹﾝｷｭｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の生理学的効果に関する研究のほとんどは、限られた集団（特定の年齢層、民族、健康状態）に焦点を当てている。今後の研究では、より広い地理的な地域にわたる多様な集団を研究することが重要である。</t>
+    <rPh sb="65" eb="68">
+      <t>ﾁﾘﾃｷ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>異なる集団の人々において、光が健康にどのように影響するのかを理解するためには、さらなる研究が必要である。</t>
+    <rPh sb="0" eb="1">
+      <t>ｺﾄ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ｼｭｳﾀﾞﾝ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ﾋﾄﾋﾞﾄ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ｹﾝｺｳ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ｴｲｷｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の生理的影響については、幅広い研究対象集団を取り入れた研究が必要である。</t>
+    <rPh sb="18" eb="20">
+      <t>ﾀｲｼｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>現実世界での光曝露を調査する研究が必要である。</t>
+    <rPh sb="0" eb="4">
+      <t>ｹﾞﾝｼﾞﾂｾｶｲ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ﾋｶﾘﾊﾞｸﾛ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の生体への影響に関する研究のほとんどは、実験室で行われてきた。</t>
+    <rPh sb="2" eb="4">
+      <t>ｾｲﾀｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の生理学的影響に関する研究のほとんどは、実験室で行われてきた。</t>
+    <rPh sb="6" eb="8">
+      <t>ｴｲｷｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光感受性の個人差は、年齢、遺伝、行動などの要因に影響される。</t>
+  </si>
+  <si>
+    <t>光に対する反応は人によって大きく異なることがある。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光に対する生理的反応にはかなりの個人差がある。</t>
+  </si>
+  <si>
+    <t>光の非視覚的作用に影響する要因（21-23）</t>
+    <rPh sb="0" eb="1">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="2" eb="8">
+      <t>ﾋｼｶｸﾃｷｻﾖｳ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ｴｲｷｮｳ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ﾖｳｲﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>加齢とともに目の水晶体の透明度が低下し、光曝露に対する生体反応が弱くなるかもしれない。</t>
+    <rPh sb="8" eb="11">
+      <t>ｽｲｼｮｳﾀｲ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ｾｲﾀｲ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ﾖﾜ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>加齢に伴い、目の水晶体の透明度が低下し、体内時計や睡眠に対する光の影響が弱まるかもしれない。</t>
+    <rPh sb="8" eb="11">
+      <t>ｽｲｼｮｳﾀｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>加齢により網膜に到達する光が少なくなるため、光の生理的作用は年齢に影響されることがある。</t>
+    <rPh sb="27" eb="29">
+      <t>ｻﾖｳ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ﾈﾝﾚｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中は明るく、夜は暗くという規則的なパターンを維持することは、より良い心身の健康状態と関連している。</t>
+    <rPh sb="16" eb="17">
+      <t>ﾃｷ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ﾖ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ｼﾞｮｳﾀｲ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ｶﾝﾚﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>健康的な生活習慣には、日中の明るい光と夜の暗闇が含まれる。</t>
+    <rPh sb="4" eb="6">
+      <t>ｾｲｶﾂ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ｼｭｳｶﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>健康的な1日の光曝露パターンには、毎日の明るい光と暗闇のリズムが含まれる。</t>
+    <rPh sb="8" eb="10">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ﾏｲﾆﾁ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>明るい光への曝露は、季節性感情障害の人の抑うつ症状が改善することが示されている。</t>
+    <rPh sb="3" eb="4">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>医師は冬季うつ病やその他の健康状態の治療として光療法を処方するかもしれない。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>医学的に処方された高照度プロトコールに従った朝の光曝露は、特定の疾患を有する人の気分の改善を促すことがある。</t>
+    <rPh sb="9" eb="12">
+      <t>ｺｳｼｮｳﾄﾞ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ｱｻ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ﾋｶﾘﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ｼｯｶﾝ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ﾕｳ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ｳﾅｶﾞ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光の非視覚的作用（10-20）</t>
+    <rPh sb="0" eb="1">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ﾋｼｶｸﾃｷ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ｻﾖｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中の高い光量への曝露は、夜の睡眠の断片化（夜中に目が覚めること）を減少させ、深い睡眠を増加させる。</t>
+    <rPh sb="3" eb="4">
+      <t>ﾀｶ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ﾖﾙ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中のより強い光曝露は、睡眠を改善することがある。</t>
+    <rPh sb="7" eb="8">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中の高い光量は、その日の夜の睡眠の質を改善することがある。</t>
+    <rPh sb="3" eb="4">
+      <t>ﾀｶ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ｺｳﾘｮｳ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ｶｲｾﾞﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然光（太陽）やまぶしくない範囲の高強度の人工光への曝露は、ストレスを軽減し、感情のバランスを改善することがある。</t>
+    <rPh sb="17" eb="20">
+      <t>ｺｳｷｮｳﾄﾞ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中の明るい光は気分を改善することがある。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中の高い光量は、気分を改善することがある。</t>
+    <rPh sb="3" eb="4">
+      <t>ﾀｶ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ｷﾌﾞﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>夕方の光曝露は、体にまだ昼間であると伝える。これにより、覚醒度が高まり、体内時計が遅い時間にシフトする。</t>
+    <rPh sb="3" eb="6">
+      <t>ﾋｶﾘﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ｶﾗﾀﾞ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ﾂﾀ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ｼﾞｺｸ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>夕方の光に曝露されると、寝つきにくくなることがある。</t>
+    <rPh sb="5" eb="7">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ﾈ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>夕方の光量が多いと、寝付くまでの時間が長くなることがある。</t>
+    <rPh sb="10" eb="12">
+      <t>ﾈﾂ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ipRGCの反応は、時刻と概日要因に依存しているようである。</t>
+    <rPh sb="10" eb="12">
+      <t>ｼﾞｺｸ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光に対する生体の反応は、光が網膜のipRGCに到達する量と時刻に依存する。</t>
+    <rPh sb="5" eb="7">
+      <t>ｾｲﾀｲ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ｼﾞｺｸ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ｲｿﾞﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光に対するこれらの生理的反応は、ある特定の時刻にどれだけの光が網膜に到達し、ipRGCを刺激するかによって主に決まる。</t>
+    <rPh sb="58" eb="59">
+      <t>ｵﾓ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ある条件下では、日中と夜間の高強度の光曝露は、覚醒度を高め、認知能力を向上させる。</t>
+    <rPh sb="14" eb="15">
+      <t>ｺｳ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ｷｮｳﾄﾞ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ある状況では、光は覚醒度と思考能力を向上させることがある。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光はまた、ある条件下では覚醒度と認知機能を高めることがある。</t>
+    <rPh sb="0" eb="1">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ｼﾞｮｳｹﾝｶ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ｶｸｾｲ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ﾄﾞ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ﾆﾝﾁ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ｷﾉｳ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ﾀｶ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光は脳に活動するように指示を出す。朝の光は体内時計を進め（早い「時刻」にシフトさせ）、夕方の光は体内時計を遅らせる（遅い「時刻」にシフトさせる）。</t>
+    <rPh sb="32" eb="34">
+      <t>ｼﾞｺｸ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ｼﾞｺｸ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝の光は就寝時刻と起床時刻を早め、夕方の光は就寝時刻と起床時刻を遅らせることがある。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝の光は概日時計を早め、夕方の光は概日時計を遅らせることがある。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光曝露は、睡眠、ホルモン分泌、代謝、覚醒に影響を与える。</t>
+    <rPh sb="0" eb="3">
+      <t>ﾋｶﾘﾊﾞｸﾛ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光は睡眠・覚醒パターンやその他の１日のリズムを調整する体内時計に影響を与える。</t>
+    <rPh sb="16" eb="18">
+      <t>ｲﾁﾆﾁ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>ﾀｲﾅｲﾄﾞｹｲ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ｴｲｷｮｳ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ｱﾀ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光は脳の体内時計に直接影響し、睡眠・覚醒サイクルやその他の1日の生理的リズムを調節する。</t>
+  </si>
+  <si>
+    <t>光は体内リズムの調整に役立つ。これにより、体内での生物学的な処理が適切な時間に始まったり止まったりするようになる。</t>
+    <rPh sb="21" eb="23">
+      <t>ﾀｲﾅｲ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ｼｮﾘ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光は、体内時計を太陽の昼夜サイクルに同調させる主要なシグナルである。</t>
+    <rPh sb="18" eb="20">
+      <t>ﾄﾞｳﾁｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光は、概日システムを環境がもつ24時間周期に同調させるための主要なシグナルである。</t>
+    <rPh sb="10" eb="12">
+      <t>ｶﾝｷｮｳ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ﾄﾞｳﾁｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ipRGCはメラノプシン（光感受性タンパク質）を発現している。ipRGCが明るい光を検出すると、メラノプシンが活性化する。この活性化によって神経経路を介した信号伝達が誘発され、松果体におけるメラトニンの生成を阻害する。</t>
+    <rPh sb="42" eb="44">
+      <t>ｹﾝｼｭﾂ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>ｶｲ</t>
+    </rPh>
+    <rPh sb="78" eb="82">
+      <t>ｼﾝｺﾞｳﾃﾞﾝﾀﾂ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ﾕｳﾊﾂ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光は、特に夕方および夜間において、メラトニン（睡眠／覚醒サイクルを調節するホルモン）の生成を阻害する。</t>
+    <rPh sb="11" eb="12">
+      <t>ｶﾝ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ｾﾂ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>主にipRGCを介して、光は夕方および夜間のメラトニンの抑制を引き起こす。</t>
+    <rPh sb="20" eb="21">
+      <t>ｶﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ipRGCは、睡眠・覚醒サイクル、覚醒度、気分を調節する脳領域に電気信号を送る。</t>
+  </si>
+  <si>
+    <t>ipRGCが光を検出すると、脳に信号を送り、さまざまな生体機能を調節する。</t>
+    <rPh sb="27" eb="29">
+      <t>ｾｲﾀｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>内因性光感受性網膜神経節細胞（ipRGC）は、光を多くの生理的機能に影響を与える信号に変換する。</t>
+    <rPh sb="0" eb="3">
+      <t>ﾅｲｲﾝｾｲ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ﾋｶﾘｶﾝｼﾞｭ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>桿体（かんたい）は低照度に対して感受性がとても高い。夜間の視力維持に欠かせない。</t>
+    <rPh sb="23" eb="24">
+      <t>ﾀｶ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>桿体細胞は、薄暗い光の下で形やその細部を見るのに役立つ。</t>
+    <rPh sb="9" eb="10">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ﾓﾄ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ｻｲﾌﾞ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>桿体によって、私たちは薄暗い光の下でもおおまかな空間的細部を見ることができる。</t>
+    <rPh sb="26" eb="27">
+      <t>ﾃｷ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ｻｲﾌﾞ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ヒトの光受容器（7-9）</t>
+    <rPh sb="3" eb="6">
+      <t>ﾋｶﾘｼﾞｭﾖｳ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ｷ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>錐体は網膜にある特殊な細胞である。その形（顕微鏡で見たときの見え方）から錐体と名づけられた。錐体の密度が最も高いのは中心窩（網膜の中心部）である。</t>
+    <rPh sb="36" eb="38">
+      <t>ｽｲﾀｲ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ﾅ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ﾁｭｳｼﾝ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>錐体細胞は、明るい光の下で色や動き、物体を見るのに役立つ。</t>
+    <rPh sb="6" eb="7">
+      <t>ｱｶ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ｼﾀ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ﾀｲ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ﾔｸﾀﾞ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>錐体によって、私たちは明るい照明の下で色、動き、空間的細部を見ることができる。</t>
+    <rPh sb="26" eb="27">
+      <t>ﾃｷ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>人間の目の網膜には、光を脳への信号に変換する光感受性細胞がある。これらの細胞は、錐体、桿体、内因性光感受性網膜神経節細胞（ipRGC）と呼ばれる。</t>
+    <rPh sb="0" eb="2">
+      <t>ﾆﾝｹﾞﾝ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ﾒ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ﾓｳﾏｸ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ﾉｳ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ｼﾝｺﾞｳ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ﾍﾝｶﾝ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>ﾋｶﾘｶﾝｼﾞｭｾｲ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ｻｲﾎﾞｳ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>ﾅｲｲﾝｾｲ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ｶﾝｼﾞｭ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>目の中の網膜には、異なる色を検出するための細胞がある。</t>
+    <rPh sb="2" eb="3">
+      <t>ﾅｶ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ﾓｳﾏｸ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ｺﾄ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ｲﾛ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ｹﾝｼｭﾂ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ｻｲﾎﾞｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>人間の目には網膜があり、そこには異なる波長に対して異なる反応を示すいくつかの光感受性細胞がある。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>太陽光が大気を通過するとき、青い光は他の波長よりも散乱される。そのため、空が青く見える。</t>
+    <rPh sb="36" eb="37">
+      <t>ｿﾗ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ｱｵ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ﾐ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>昼光の色、強さ、パターンは、一日を通して季節や天候によって変化する。</t>
+    <rPh sb="0" eb="2">
+      <t>ﾁｭｳｺｳ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ｲﾁﾆﾁ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ﾄｵ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>昼光の特性（スペクトル、強度、空間分布）は、一日および一年を通して、また天候の変化によって変化する。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光と分光特性（1-6）</t>
+    <rPh sb="0" eb="1">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>異なる光源技術には、電気を光に変換するために</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>異</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>様々な材料が使用されている。材料が異なると、光の強度が波長ごとに異なる形で分布する。この波長全体にわたる光の広がりは、分光分布として知られている。</t>
+    </r>
+  </si>
+  <si>
+    <t>異なる光源は異なる方法で光を発生させ、異なる波長や色を作り出す。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>異なる電気光源（LEDや蛍光灯など）は異なるスペクトルを持つ。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>直射日光と散乱光の組み合わせである昼光は、すべての可視波長とそれ以外の波長を含んでいる。時間帯や天候の変化によって波長の構成は変化する。この変化により、昼光の色が変化する。</t>
+    <rPh sb="0" eb="2">
+      <t>ﾁｮｸｼｬ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ｲｶﾞｲ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ﾁｭｳｺｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>昼光は様々なエネルギーを持つ複数の波長で構成されており、虹のすべての色に分けることができる。</t>
+    <rPh sb="0" eb="2">
+      <t>ﾁｭｳｺｳ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ｻﾏｻﾞﾏ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ﾓ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ｺｳｾｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日中の光（昼光）は広域スペクトルと呼ばれ、多くの波長にわたって多くのエネルギーを持つ。</t>
+    <rPh sb="0" eb="2">
+      <t>ﾆｯﾁｭｳ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ｺｳ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ﾁｭｳｺｳ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ｺｳｲｷ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ﾖ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光源は、各波長においてどれだけのエネルギーを放出しているかによって特徴づけられる。このエネルギーは「強度（intensity）」と呼ばれる。物理学者はこの強度を測定し、生物学者や心理学者は光の強度がさまざまなプロセスに及ぼす影響を研究する。</t>
+    <rPh sb="94" eb="95">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>光曝露量は、様々な波長での光の強さを測定することで評価できる。</t>
+    <rPh sb="0" eb="4">
+      <t>ﾋｶﾘﾊﾞｸﾛﾘｮｳ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ｻﾏｻﾞﾏ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ｿｸﾃｲ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ﾋｮｳｶ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>光曝露量はその強度によって</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>表すことができる： 380～780nmの全波長にわたるエネルギーの総量で、関心のある機能に応じて重み付けされる。</t>
+    </r>
+  </si>
+  <si>
+    <t>太陽からの光は夜明けから真昼にかけて増加し、夕方になると減少する。場所にもよるが、1日の光量は夏と冬で大きく異なる。</t>
+  </si>
+  <si>
+    <t>私たちの周りにある光の量（あるいは私たちが曝露される光の量）は、屋内と屋外の行き来や一日の時間帯、そして季節によって変化する。</t>
+    <rPh sb="21" eb="23">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>ｼﾞｶﾝﾀｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>一日を通して、また一年を通しての光曝露のパターンは非常に複雑で、どこにいるか、何をしているかによって異なる。</t>
+    <rPh sb="17" eb="19">
+      <t>ﾊﾞｸﾛ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>私たちが異なる色を見るとき、実際には異なる波長の光を見ている。短い波長は紫色に見え、波長が長くなるにつれて藍色、青色、緑色、黄色、オレンジ色、赤色に見える。</t>
+    <rPh sb="18" eb="19">
+      <t>ｺﾄ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ﾊﾁｮｳ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ﾊﾁｮｳ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>白色光は、私たちが色として認識している複数の波長で構成されている。</t>
+    <rPh sb="0" eb="2">
+      <t>ﾊｸｼｮｸ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ﾜﾀｼ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ｲﾛ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ﾆﾝｼｷ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ﾌｸｽｳ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ﾊﾁｮｳ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ｺｳｾｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>光は分光特性によって</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>表すことができる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：可視光領域（約380-780 nm）のそれぞれの波長のエネルギーがどのくらい含まれているか</t>
+    </r>
+  </si>
+  <si>
+    <t>光と分光特性（1-6）</t>
+    <rPh sb="0" eb="1">
+      <t>ﾋｶﾘ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ﾌﾞﾝｺｳ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ﾄｸｾｲ</t>
+    </rPh>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>参考文献</t>
+  </si>
+  <si>
+    <t>El interés científico y popular por los efectos de la luz sobre los ritmos biológicos, el sueño, el estado de alerta, el estado de ánimo y la salud está creciendo. Los avances tecnológicos y científicos permiten a los investigadores estudiar con mayor precisión diferentes longitudes de onda e intensidades.</t>
+  </si>
+  <si>
+    <t>Los científicos continúan investigando cómo la luz afecta a las funciones corporales y la salud en general.</t>
+  </si>
+  <si>
+    <t>El efecto fisiológico de la luz es un área de investigación activa.</t>
+  </si>
+  <si>
+    <t>Investigación sobre los efectos no visuales de la luz</t>
+  </si>
+  <si>
+    <t>La mayoría de los estudios sobre los efectos fisiológicos de la luz se han centrado en poblaciones limitadas (grupos de edad, etnias o condiciones de salud específicos). Es importante que las investigaciones futuras estudien poblaciones más diversas en más regiones geográficas.</t>
+  </si>
+  <si>
+    <t>Se necesitan más estudios para comprender cómo influye la luz en la salud de diferentes grupos de personas.</t>
+  </si>
+  <si>
+    <t>Es necesario realizar estudios sobre los efectos fisiológicos de la luz que incorporen una amplia gama de poblaciones de estudio.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Se necesitan estudios que investiguen la exposici</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF741B47"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ón</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> a la luz en el mundo real.</t>
+    </r>
+  </si>
+  <si>
+    <t>La mayoría de las investigaciones sobre los efectos de la luz en el cuerpo se han llevado a cabo en el laboratorio.</t>
+  </si>
+  <si>
+    <t>La mayoría de los estudios sobre los efectos fisiológicos de la luz se han realizado en el laboratorio.</t>
+  </si>
+  <si>
+    <t>Las diferencias individuales en la sensibilidad a la luz están influidas por factores como la edad, la genética y el comportamiento.</t>
+  </si>
+  <si>
+    <t>La forma en que las personas responden a la luz puede variar mucho.</t>
+  </si>
+  <si>
+    <t>Hay importantes diferencias individuales en la respuesta fisiológica a la luz.</t>
+  </si>
+  <si>
+    <t>Factores que influyen en los efectos no visuales de la luz (21-23)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Con la edad, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>el cristalino</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de los ojos se vuelve menos transparentes, lo que puede reducir la respuesta </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">del </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>cuerpo a la exposición a la luz.</t>
+    </r>
+  </si>
+  <si>
+    <t>Con la edad, el cristalino del ojo puede perder transparencia, lo que puede reducir los efectos de la luz sobre el reloj interno y el sueño.</t>
+  </si>
+  <si>
+    <t>El efecto fisiológico de la luz en los seres humanos puede verse influido por la edad, ya que con el envejecimiento llega menos luz a la retina.</t>
+  </si>
+  <si>
+    <t>Mantener un patrón regular de luz brillante durante el día y oscuridad durante la noche se asocia con una mejor salud física y mental.</t>
+  </si>
+  <si>
+    <t>Una rutina diaria saludable incluye luz brillante durante el día y oscuridad por la noche.</t>
+  </si>
+  <si>
+    <t>Un patrón saludable de exposición diaria a la luz incluye un ritmo de luz brillante y oscuridad todos los días.</t>
+  </si>
+  <si>
+    <t>Se ha demostrado que la exposición a la luz brillante mejora los síntomas depresivos en personas con trastorno afectivo estacional.</t>
+  </si>
+  <si>
+    <t>Los médicos pueden prescribir la terapia lumínica como tratamiento para la depresión invernal y otras afecciones de salud.</t>
+  </si>
+  <si>
+    <t>Seguir un protocolo médico prescrito sobre la luz brillante, la exposición por la mañana puede conducir a mejoras en el estado de ánimo de las personas con ciertos diagnósticos clínicos.</t>
+  </si>
+  <si>
+    <t>Efectos no visuales de la luz</t>
+  </si>
+  <si>
+    <t>La exposición a niveles de luz más altos durante el día reduce la fragmentación del sueño (despertares durante la noche) y aumenta el sueño profundo por la noche.</t>
+  </si>
+  <si>
+    <t>Una exposición a una luz más intensa durante el día puede mejorar el sueño.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unos niveles de luz más altos durante el día pueden mejorar la calidad del sueño en la noche siguiente. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Exponerse a la luz natural (el sol) o a luz eléctrica de alta intensidad, puede reducir el estrés y mejorar el equilibrio emocional, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1C4587"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>siempre que se evite el deslumbramiento.</t>
+    </r>
+  </si>
+  <si>
+    <t>Una luz brillante durante el día puede mejorar el estado de ánimo.</t>
+  </si>
+  <si>
+    <t>Unos niveles de luz más altos durante el día pueden mejorar el estado de ánimo.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La exposición a la luz </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1C4587"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">en horario nocturno </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>le indica al cuerpo que aún es de día. Esto aumenta el estado de alerta y retrasa el reloj interno.</t>
+    </r>
+  </si>
+  <si>
+    <t>Exponerse a la luz por la noche puede dificultar conciliar el sueño.</t>
+  </si>
+  <si>
+    <t>Niveles altos de luz durante la noche pueden aumentar el tiempo que es necesario para conciliar el sueño.</t>
+  </si>
+  <si>
+    <t>Probablemente, la respuesta de las ipRGCs depende de la hora del día y de factores circadianos</t>
+  </si>
+  <si>
+    <t>La respuesta corporal a la luz depende de la cantidad de luz y del momento en que esta llega a las ipRGCs en la retina</t>
+  </si>
+  <si>
+    <t>Lo que determina las respuestas fisiológicas a la luz depende principalmente de la cantidad de luz que llega a la retina y estimula las ipRGCs en un momento determinado</t>
+  </si>
+  <si>
+    <t>En determinadas condiciones, la exposición a luz de alta intensidad durante el día y la noche mejora el estado de alerta y el rendimiento intelectual.</t>
+  </si>
+  <si>
+    <t>En determinadas situaciones, la luz puede mejorar el estado de alerta y la capacidad de pensar.</t>
+  </si>
+  <si>
+    <t>La luz también puede mejorar el estado de alerta y la función cognitiva, en determinadas condiciones.</t>
+  </si>
+  <si>
+    <t>La luz le indica al cerebro que se active. La luz de la mañana adelanta el reloj interno del cuerpo (lo adelanta a una «hora» más temprana), mientras que la luz de la tarde lo retrasa (lo retrasa a una «hora» más tardía).</t>
+  </si>
+  <si>
+    <t>La luz matutina favorece acostarse y levantarse más temprano, mientras que la luz vespertina puede retrasar la hora de acostarse y levantarse.</t>
+  </si>
+  <si>
+    <t>Luz en la mañana puede adelantar el reloj circadiano, y luz a la tarde puede retrasarlo.</t>
+  </si>
+  <si>
+    <t>La exposición a la luz influye en el sueño, la liberación de hormonas, el metabolismo y el estado de alerta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La luz influye en el reloj interno del cuerpo, que regula los patrones de sueño-vigilia y otros ritmos diarios. </t>
+  </si>
+  <si>
+    <t>La luz influye directamente al reloj biológico del cerebro, regulando asi los ciclos de sueño-vigilia y otros ritmos fisiológicos diarios.</t>
+  </si>
+  <si>
+    <t>La luz ayuda a regular los ritmos internos del cuerpo. Esto garantiza que los procesos biológicos se inicien y se detengan en el momento mas adecuado.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La luz es la principal señal que sincroniza el reloj interno del cuerpo con el ciclo diurno-nocturno </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF741B47"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(día-noche)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> del sol.</t>
+    </r>
+  </si>
+  <si>
+    <t>La luz es la señal principal que garantiza que el sistema circadiano esté sincronizado con los ciclos de 24 horas del ambiente externo.</t>
+  </si>
+  <si>
+    <t>Las células ipRGC expresan melanopsina (una proteína sensible a la luz). Cuando las células ipRGC detectan luz brillante, la melanopsina se activa. Esta activación desencadena una vía neuronal que bloquea la producción de melatonina en la glándula pineal.</t>
+  </si>
+  <si>
+    <t>La luz bloquea la producción de melatonina (una hormona que regula los ciclos de sueño-vigilia), especialmente por la tarde y por la noche.</t>
+  </si>
+  <si>
+    <t>La luz provoca la supresión de la melatonina por la tarde y por la noche, principalmente a través de las ipRGC.</t>
+  </si>
+  <si>
+    <t>Las ipRGCs envían señales eléctricas a las regiones del cerebro que regulan los ciclos de sueño-vigilia, estados de alerta y estado anímico.</t>
+  </si>
+  <si>
+    <t>Cuando las ipRGCs detectan la luz, envían señales eléctricas al cerebro para regular varias funciones corporales</t>
+  </si>
+  <si>
+    <t>Las células ganglionares retinianas intrínsecamente fotosensibles convierten la luz en señales que influyen en muchas funciones fisiológicas</t>
+  </si>
+  <si>
+    <t>Los bastones son muy sensibles a los niveles de luz bajos. Son esenciales para la visión nocturna</t>
+  </si>
+  <si>
+    <t>Los bastones nos permiten ver formas y detalles con luz ténue</t>
+  </si>
+  <si>
+    <t>Los bastones nos permiten ver de manera rudiemntaria los detalles espaciales con luz ténue</t>
+  </si>
+  <si>
+    <t>Fotoreceptores humanos</t>
+  </si>
+  <si>
+    <t>Los conos son células especializadas de la retina. Reciben este nombre por su forma (cómo se ven al microscopio). La mayor densidad de conos se encuentra en la fóvea (en el centro de la retina)</t>
+  </si>
+  <si>
+    <t>Los conos nos permiten ver los colores, el movimiento y los objetos con luz brillante</t>
+  </si>
+  <si>
+    <t>Los conos nos permiten ver el color, el movimiento y los detalles espaciales en condiciones de iluminación brillante</t>
+  </si>
+  <si>
+    <t>En el ojo humano, la retina tiene unas células sensibles a la luz que convierten la luz en señales para el cerebro. Estas células se denominan conos, bastones y células ganglionares retinianas intrínsecamente fotosensibles (ipRGCs)</t>
+  </si>
+  <si>
+    <t>En el ojo, la retina tiene unas células fotorreceptoras, que nos permiten detectar los diferentes colores del espectro visible</t>
+  </si>
+  <si>
+    <t>La retina está ubicada en el ojo humano que tiene varias células fotosensibles que difieren en su respuesta a diferentes longitudes de onda</t>
+  </si>
+  <si>
+    <t>A medida que la luz solar atraviesa la atmósfera, la luz azul se dispersa más que otras longitudes de onda. Esto es lo que hace que el cielo se vea azul</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">El color, la intensidad y el patrón de la luz diurna cambia a lo largo del día, con las estaciones </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF741B47"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>del año</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y el tiempo atmosférico.</t>
+    </r>
+  </si>
+  <si>
+    <t>Las propiedades de la luz diurna (espectro, intensidad y distribución espacial) varía a lo largo del día y del año y con los cambios meteorológicos</t>
+  </si>
+  <si>
+    <t>Luz y espectro</t>
+  </si>
+  <si>
+    <t>Las distintas tecnologías de las fuentes de luz emplean distintos materiales con los que convierten la electricidad en luz. Estos diferentes materiales provocan que la intensidad de luz sea emitida en diferentes distribuciones espectrales, que son las combinaciones de contenido de energía en los rangos de longitud de onda de la luz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las distintas fuentes de luz emiten radiación visible de formas diversas, dando lugar a distintas tonalidades de color o longitudes de onda. </t>
+  </si>
+  <si>
+    <t>Diferentes fuentes de luz eléctrica artificial (como las lámparas de incandescencia, las lámparas de descarga o las fuentes de luz LED) presentan diferentes distribuciones espectrales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La luz diurna, que es una combinación de radiación solar directa y luz dispersada por la atmósfera, contiene energía en bandas espectrales más allá de todas las radiaciones visibles del espectro electromagnético. </t>
+  </si>
+  <si>
+    <t>La luz diurna contiene energía distribuida en un un amplio rango de longitudes de onda, y puede descomponerse en en todos los colores del arco iris.</t>
+  </si>
+  <si>
+    <t>La luz diurna está compuesta de un espectro amplio, con una gran cantidad de energía distribuída de forma contínua en multitud de longitudes de onda del espectro visible.</t>
+  </si>
+  <si>
+    <t>Se puede caracterizar una fuente de luz cuantificando la cantidad de potencia que emite en un determinado rango de frecuencias. Esta potencia es lo que denominamos intensidad. Los físicos miden la intensidad de la fuente de luz, mientras que los biólogos y los fisiólogos estudian el impacto de dicha intensidad en varios procesos de los organismos vivos.</t>
+  </si>
+  <si>
+    <t>Se puede medir la exposición a la luz verificando la intensidad de la luz en diferentes rangos de longitud de onda.</t>
+  </si>
+  <si>
+    <t>La exposición a la luz puede ser descrita por su intensidad: la energía total distribuida entre todas las frecuencias del espectro visible, desde los 380nm a los 780nm, y ponderadas de acuerdo a la función de interés.</t>
+  </si>
+  <si>
+    <t>La energía de la radiación solar en la Tierra aumenta desde el amanecer hasta el medidodía y desciende durante la tarde. Dependiendo de la distancia al ecuador terrestre (latitud), la cantidad de luz diurna varía de forma muy significativa entre el verano y el invierno.</t>
+  </si>
+  <si>
+    <t>La cantidad de luz que nos rodea, aquella a la que nos vemos expuestos, cambia mientras nos desplazamos entre los entornos interiores y los espacios exteriores, cambia durante el día y cambia a lo largo de las estaciones del año.</t>
+  </si>
+  <si>
+    <t>Establecer el patrón de exposición a la luz durante un día o un año año puede ser una tarea compleja, y depende de la localización geográfica y de la actividad diaria.</t>
+  </si>
+  <si>
+    <t>Cuando percibimos diferentes colores, estamos realmente viendo diferentes longitudes de onda de la luz. Las longitudes de onda cortas corresponden con la apariencia del color violeta, mientras que las longitudes de onda más largas tienen la apariencia de color indigo, azul, verde, amarillo, naranja y rojo.</t>
+  </si>
+  <si>
+    <t>La luz blanca es el resultado de la aportación de multitud de longitudes de onda, que nosotros percibimos como colores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La luz puede ser definida por su espectro, que informa acerca de la cantidad de energía presente en cada longitud de onda del espectro visible (desde aproximadamente 380nm hasta los 780nm) </t>
+  </si>
+  <si>
+    <t>Referencias</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Declaración</t>
+  </si>
+  <si>
+    <t>Declaración simplificada</t>
+  </si>
+  <si>
+    <t>Información contextual</t>
+  </si>
+  <si>
+    <t>陳述</t>
+  </si>
+  <si>
+    <t>番号</t>
+  </si>
+  <si>
+    <t>章</t>
+  </si>
+  <si>
+    <t>簡略化された陳述</t>
+  </si>
+  <si>
+    <t>文脈情報</t>
+  </si>
+  <si>
+    <t>光は、概日リズムや睡眠、気分、認知機能に影響を与える、生体にとっての強力なシグナルです。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガイジツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キブン</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ニンチキノウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セイタイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>キョウリョク</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>光がどのくらい明るいかだけではなく、「いつ」、「どのような種類」の光かが重要です。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>朝や日中の光は健康をサポートしますが、夜の光は健康を乱すことがあります。</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニッチュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヨル</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ミダ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>夕方の低い光量と睡眠中の暗闇は、健康的な明暗リズムの一部です。</t>
+    <rPh sb="0" eb="2">
+      <t>ユウガタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>スイミンチュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>クラヤミ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ケンコウテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メイアン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>光曝露を管理することは、食事や運動、睡眠衛生と同様に、健康的なライフスタイルの一部です。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>バクロ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショクジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ウンドウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>エイセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>Higuchi</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shigekazu</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ph.D.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>higu-s@design.kyushu-u.ac.jp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kyushu University</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0000-0001-7131-0792</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eto</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taisuke</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>taisuke.eto.820@gmail.com</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keio University</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0000-0002-0347-7408</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La luz es una señal potente para el organismo, ya que afecta a nuestros ritmos circadianos, a la calidad del sueño, al estado de ánimo y al rendimiento </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1C4587"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>intelectual</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>No se trata solo de la intensidad de la luz: también importa cuándo y qué tipo de luz se utiliza.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La luz natural durante la mañana y el día favorece aspectos relacionados con la salud, mientras que </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF134F5C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>la exposición a la luz artificial en horario nocturno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> puede resultar disruptora.</t>
+    </r>
+  </si>
+  <si>
+    <t>Unos niveles de luz bajos por la noche y oscuridad mientras dormimos forman parte de un ritmo de luz y oscuridad saludable.</t>
+  </si>
+  <si>
+    <t>La gestión de la exposición a la luz forma parte de un estilo de vida saludable, al igual que la dieta, el ejercicio y la higiene del sueño.</t>
+  </si>
+  <si>
+    <t>Fambuena-Muedra</t>
+  </si>
+  <si>
+    <t>Isabel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
+        <rFont val="Calibri, sans-serif"/>
+      </rPr>
+      <t>isabellafamu@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>Universitat de València</t>
+  </si>
+  <si>
+    <t>0000-0002-8828-927X</t>
+  </si>
+  <si>
+    <t>Gimenez</t>
+  </si>
+  <si>
+    <t>Marina</t>
+  </si>
+  <si>
+    <t>marina.gimenez@gmail.com</t>
+  </si>
+  <si>
+    <t>University of Groningen &amp; Chrono@Work</t>
+  </si>
+  <si>
+    <t>0000-0002-2286-8850</t>
+  </si>
+  <si>
+    <t>Barberá Duelo</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>ab@natura-urbana.org</t>
+  </si>
+  <si>
+    <t>CICAT - Catalonia Lighting Cluster</t>
+  </si>
+  <si>
+    <t>0009-0008-1046-2256</t>
+  </si>
+  <si>
+    <t>Sanchez-Herrera</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>MsC</t>
+  </si>
+  <si>
+    <t>davids.herrera1@gmail.com</t>
+  </si>
+  <si>
+    <t>INCAN-National Institute of Cancerology</t>
+  </si>
+  <si>
+    <t>0009-0006-2622-3642</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="85">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-3000401]0"/>
+  </numFmts>
+  <fonts count="114">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -7878,6 +9582,193 @@
       <color rgb="FF000000"/>
       <name val="Open Sans Bold"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF242424"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri Light"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri Light"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF70AD46"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF741B47"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF741B47"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C4587"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF70AD47"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF70AD47"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C4587"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF134F5C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF70AD46"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF70AD46"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF70AD46"/>
+      <name val="Calibri, sans-serif"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF70AD47"/>
+      <name val="Noto Sans"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF741B47"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF741B47"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -8090,7 +9981,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -8437,8 +10328,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="45">
+  <cellStyleXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -8486,8 +10390,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8838,8 +10743,127 @@
     <xf numFmtId="0" fontId="73" fillId="35" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="85" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="86" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="45" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="36" borderId="25" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="36" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="21" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="36" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="36" borderId="19" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="36" borderId="19" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="36" borderId="19" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="36" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="36" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="36" borderId="19" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="36" borderId="19" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="36" borderId="22" xfId="45" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="71" fillId="36" borderId="19" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="45">
+  <cellStyles count="46">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -8877,6 +10901,7 @@
     <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="43" xr:uid="{70AE8D79-DF60-5941-BC6B-2804C19A889C}"/>
+    <cellStyle name="Standard 3" xfId="45" xr:uid="{8B4721E8-5972-E240-9A1E-9870DCB1569C}"/>
     <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
@@ -9751,6 +11776,2354 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04711008-D18A-0842-8C2B-205459E35B17}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="42.33203125" style="141" customWidth="1"/>
+    <col min="5" max="5" width="42.33203125" style="140" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="34" customFormat="1" ht="85">
+      <c r="A2" s="144" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B2" s="31">
+        <v>1</v>
+      </c>
+      <c r="C2" s="153" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D2" s="154" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E2" s="145" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="68">
+      <c r="A3" s="144" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B3" s="31">
+        <v>2</v>
+      </c>
+      <c r="C3" s="153" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E3" s="151" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="102">
+      <c r="A4" s="144" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B4" s="31">
+        <v>3</v>
+      </c>
+      <c r="C4" s="150" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D4" s="146" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E4" s="149" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="94.5" customHeight="1">
+      <c r="A5" s="144" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B5" s="31">
+        <v>4</v>
+      </c>
+      <c r="C5" s="146" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D5" s="146" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E5" s="147" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="102">
+      <c r="A6" s="144" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B6" s="31">
+        <v>5</v>
+      </c>
+      <c r="C6" s="148" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D6" s="146" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E6" s="145" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="51">
+      <c r="A7" s="144" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B7" s="31">
+        <v>6</v>
+      </c>
+      <c r="C7" s="146" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D7" s="146" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E7" s="147" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="68">
+      <c r="A8" s="144" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B8" s="31">
+        <v>7</v>
+      </c>
+      <c r="C8" s="146" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D8" s="146" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E8" s="145" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="68">
+      <c r="A9" s="144" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B9" s="31">
+        <v>8</v>
+      </c>
+      <c r="C9" s="146" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D9" s="146" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E9" s="147" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="51">
+      <c r="A10" s="144" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B10" s="31">
+        <v>9</v>
+      </c>
+      <c r="C10" s="146" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D10" s="146" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E10" s="145" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="69.75" customHeight="1">
+      <c r="A11" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B11" s="31">
+        <v>10</v>
+      </c>
+      <c r="C11" s="146" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D11" s="146" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E11" s="147" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="102">
+      <c r="A12" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B12" s="31">
+        <v>11</v>
+      </c>
+      <c r="C12" s="146" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D12" s="146" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E12" s="145" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51">
+      <c r="A13" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B13" s="31">
+        <v>12</v>
+      </c>
+      <c r="C13" s="146" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D13" s="146" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E13" s="147" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="51">
+      <c r="A14" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B14" s="31">
+        <v>13</v>
+      </c>
+      <c r="C14" s="146" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D14" s="146" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E14" s="147" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="68">
+      <c r="A15" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B15" s="31">
+        <v>14</v>
+      </c>
+      <c r="C15" s="146" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D15" s="146" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E15" s="147" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="59.25" customHeight="1">
+      <c r="A16" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B16" s="31">
+        <v>15</v>
+      </c>
+      <c r="C16" s="146" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D16" s="146" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E16" s="145" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="51">
+      <c r="A17" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B17" s="31">
+        <v>16</v>
+      </c>
+      <c r="C17" s="146" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D17" s="146" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E17" s="145" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="51">
+      <c r="A18" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B18" s="31">
+        <v>17</v>
+      </c>
+      <c r="C18" s="146" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D18" s="146" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E18" s="147" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="51">
+      <c r="A19" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B19" s="31">
+        <v>18</v>
+      </c>
+      <c r="C19" s="146" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D19" s="146" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E19" s="145" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="51">
+      <c r="A20" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B20" s="31">
+        <v>19</v>
+      </c>
+      <c r="C20" s="146" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D20" s="146" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E20" s="145" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="51">
+      <c r="A21" s="144" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B21" s="31">
+        <v>20</v>
+      </c>
+      <c r="C21" s="146" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D21" s="146" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E21" s="145" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="51">
+      <c r="A22" s="144" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B22" s="31">
+        <v>21</v>
+      </c>
+      <c r="C22" s="146" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D22" s="146" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E22" s="145" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="69" customHeight="1">
+      <c r="A23" s="144" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B23" s="31">
+        <v>22</v>
+      </c>
+      <c r="C23" s="146" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D23" s="146" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E23" s="145" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="63.75" customHeight="1">
+      <c r="A24" s="144" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B24" s="31">
+        <v>23</v>
+      </c>
+      <c r="C24" s="146" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D24" s="146" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E24" s="147" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="55.5" customHeight="1">
+      <c r="A25" s="144" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B25" s="31">
+        <v>24</v>
+      </c>
+      <c r="C25" s="146" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D25" s="146" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E25" s="147" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="105" customHeight="1">
+      <c r="A26" s="144" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B26" s="31">
+        <v>25</v>
+      </c>
+      <c r="C26" s="146" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D26" s="146" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E26" s="145" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="122.25" customHeight="1" thickBot="1">
+      <c r="A27" s="144" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B27" s="28">
+        <v>26</v>
+      </c>
+      <c r="C27" s="143" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D27" s="143" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E27" s="142" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E52B6AF-BAC7-C845-97B2-04E72B329E71}">
+  <dimension ref="A1:V1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="19.5" style="155" customWidth="1"/>
+    <col min="2" max="2" width="7.83203125" style="155" customWidth="1"/>
+    <col min="3" max="5" width="32.83203125" style="155" customWidth="1"/>
+    <col min="6" max="22" width="8.83203125" style="155" customWidth="1"/>
+    <col min="23" max="16384" width="11.1640625" style="155"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="283.5" customHeight="1">
+      <c r="A2" s="160" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B2" s="171">
+        <v>1</v>
+      </c>
+      <c r="C2" s="169" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D2" s="169" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E2" s="168" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="172"/>
+      <c r="U2" s="172"/>
+      <c r="V2" s="172"/>
+    </row>
+    <row r="3" spans="1:22" ht="136">
+      <c r="A3" s="160" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B3" s="171">
+        <v>2</v>
+      </c>
+      <c r="C3" s="169" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D3" s="169" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E3" s="168" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="187">
+      <c r="A4" s="160" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B4" s="171">
+        <v>3</v>
+      </c>
+      <c r="C4" s="169" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D4" s="169" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E4" s="170" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="119">
+      <c r="A5" s="160" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B5" s="163">
+        <v>4</v>
+      </c>
+      <c r="C5" s="169" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D5" s="169" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E5" s="168" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="170">
+      <c r="A6" s="160" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B6" s="163">
+        <v>5</v>
+      </c>
+      <c r="C6" s="169" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D6" s="169" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E6" s="168" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="85">
+      <c r="A7" s="160" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B7" s="163">
+        <v>6</v>
+      </c>
+      <c r="C7" s="158" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D7" s="166" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E7" s="167" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="136">
+      <c r="A8" s="160" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B8" s="163">
+        <v>7</v>
+      </c>
+      <c r="C8" s="158" t="s">
+        <v>1629</v>
+      </c>
+      <c r="D8" s="166" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E8" s="167" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="102">
+      <c r="A9" s="160" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B9" s="163">
+        <v>8</v>
+      </c>
+      <c r="C9" s="158" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D9" s="166" t="s">
+        <v>1625</v>
+      </c>
+      <c r="E9" s="167" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="51">
+      <c r="A10" s="160" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B10" s="163">
+        <v>9</v>
+      </c>
+      <c r="C10" s="158" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D10" s="166" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E10" s="161" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="85">
+      <c r="A11" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B11" s="163">
+        <v>10</v>
+      </c>
+      <c r="C11" s="166" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D11" s="166" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E11" s="164" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="136">
+      <c r="A12" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B12" s="163">
+        <v>11</v>
+      </c>
+      <c r="C12" s="158" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D12" s="158" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E12" s="164" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="85">
+      <c r="A13" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B13" s="163">
+        <v>12</v>
+      </c>
+      <c r="C13" s="162" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D13" s="158" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E13" s="162" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="68">
+      <c r="A14" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B14" s="163">
+        <v>13</v>
+      </c>
+      <c r="C14" s="162" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D14" s="158" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E14" s="164" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="119">
+      <c r="A15" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B15" s="163">
+        <v>14</v>
+      </c>
+      <c r="C15" s="162" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D15" s="165" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E15" s="164" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="85">
+      <c r="A16" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B16" s="163">
+        <v>15</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D16" s="165" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E16" s="162" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="85">
+      <c r="A17" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B17" s="163">
+        <v>16</v>
+      </c>
+      <c r="C17" s="158" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D17" s="158" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="164" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="68">
+      <c r="A18" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B18" s="163">
+        <v>17</v>
+      </c>
+      <c r="C18" s="162" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D18" s="165" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E18" s="162" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="85">
+      <c r="A19" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B19" s="163">
+        <v>18</v>
+      </c>
+      <c r="C19" s="158" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D19" s="165" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E19" s="164" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="102">
+      <c r="A20" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B20" s="163">
+        <v>19</v>
+      </c>
+      <c r="C20" s="158" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D20" s="165" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E20" s="164" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="102">
+      <c r="A21" s="160" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B21" s="163">
+        <v>20</v>
+      </c>
+      <c r="C21" s="158" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D21" s="165" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E21" s="164" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="85">
+      <c r="A22" s="160" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B22" s="163">
+        <v>21</v>
+      </c>
+      <c r="C22" s="158" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D22" s="165" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E22" s="164" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="85">
+      <c r="A23" s="160" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B23" s="163">
+        <v>22</v>
+      </c>
+      <c r="C23" s="158" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D23" s="165" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E23" s="162" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="85">
+      <c r="A24" s="160" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B24" s="163">
+        <v>23</v>
+      </c>
+      <c r="C24" s="158" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D24" s="158" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E24" s="164" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="68">
+      <c r="A25" s="160" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B25" s="163">
+        <v>24</v>
+      </c>
+      <c r="C25" s="162" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D25" s="165" t="s">
+        <v>1574</v>
+      </c>
+      <c r="E25" s="164" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="153">
+      <c r="A26" s="160" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B26" s="163">
+        <v>25</v>
+      </c>
+      <c r="C26" s="162" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D26" s="158" t="s">
+        <v>1571</v>
+      </c>
+      <c r="E26" s="161" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="154" thickBot="1">
+      <c r="A27" s="160" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B27" s="159">
+        <v>26</v>
+      </c>
+      <c r="C27" s="158" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D27" s="158" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E27" s="157" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E28" s="156"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E29" s="156"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E30" s="156"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E31" s="156"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E32" s="156"/>
+    </row>
+    <row r="33" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E33" s="156"/>
+    </row>
+    <row r="34" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E34" s="156"/>
+    </row>
+    <row r="35" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E35" s="156"/>
+    </row>
+    <row r="36" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E36" s="156"/>
+    </row>
+    <row r="37" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E37" s="156"/>
+    </row>
+    <row r="38" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E38" s="156"/>
+    </row>
+    <row r="39" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E39" s="156"/>
+    </row>
+    <row r="40" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E40" s="156"/>
+    </row>
+    <row r="41" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E41" s="156"/>
+    </row>
+    <row r="42" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E42" s="156"/>
+    </row>
+    <row r="43" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E43" s="156"/>
+    </row>
+    <row r="44" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E44" s="156"/>
+    </row>
+    <row r="45" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E45" s="156"/>
+    </row>
+    <row r="46" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E46" s="156"/>
+    </row>
+    <row r="47" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E47" s="156"/>
+    </row>
+    <row r="48" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E48" s="156"/>
+    </row>
+    <row r="49" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E49" s="156"/>
+    </row>
+    <row r="50" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E50" s="156"/>
+    </row>
+    <row r="51" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E51" s="156"/>
+    </row>
+    <row r="52" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E52" s="156"/>
+    </row>
+    <row r="53" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E53" s="156"/>
+    </row>
+    <row r="54" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E54" s="156"/>
+    </row>
+    <row r="55" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E55" s="156"/>
+    </row>
+    <row r="56" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E56" s="156"/>
+    </row>
+    <row r="57" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E57" s="156"/>
+    </row>
+    <row r="58" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E58" s="156"/>
+    </row>
+    <row r="59" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E59" s="156"/>
+    </row>
+    <row r="60" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E60" s="156"/>
+    </row>
+    <row r="61" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E61" s="156"/>
+    </row>
+    <row r="62" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E62" s="156"/>
+    </row>
+    <row r="63" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E63" s="156"/>
+    </row>
+    <row r="64" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E64" s="156"/>
+    </row>
+    <row r="65" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E65" s="156"/>
+    </row>
+    <row r="66" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E66" s="156"/>
+    </row>
+    <row r="67" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E67" s="156"/>
+    </row>
+    <row r="68" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E68" s="156"/>
+    </row>
+    <row r="69" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E69" s="156"/>
+    </row>
+    <row r="70" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E70" s="156"/>
+    </row>
+    <row r="71" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E71" s="156"/>
+    </row>
+    <row r="72" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E72" s="156"/>
+    </row>
+    <row r="73" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E73" s="156"/>
+    </row>
+    <row r="74" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E74" s="156"/>
+    </row>
+    <row r="75" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E75" s="156"/>
+    </row>
+    <row r="76" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E76" s="156"/>
+    </row>
+    <row r="77" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E77" s="156"/>
+    </row>
+    <row r="78" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E78" s="156"/>
+    </row>
+    <row r="79" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E79" s="156"/>
+    </row>
+    <row r="80" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E80" s="156"/>
+    </row>
+    <row r="81" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E81" s="156"/>
+    </row>
+    <row r="82" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E82" s="156"/>
+    </row>
+    <row r="83" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E83" s="156"/>
+    </row>
+    <row r="84" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E84" s="156"/>
+    </row>
+    <row r="85" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E85" s="156"/>
+    </row>
+    <row r="86" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E86" s="156"/>
+    </row>
+    <row r="87" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E87" s="156"/>
+    </row>
+    <row r="88" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E88" s="156"/>
+    </row>
+    <row r="89" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E89" s="156"/>
+    </row>
+    <row r="90" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E90" s="156"/>
+    </row>
+    <row r="91" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E91" s="156"/>
+    </row>
+    <row r="92" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E92" s="156"/>
+    </row>
+    <row r="93" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E93" s="156"/>
+    </row>
+    <row r="94" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E94" s="156"/>
+    </row>
+    <row r="95" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E95" s="156"/>
+    </row>
+    <row r="96" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E96" s="156"/>
+    </row>
+    <row r="97" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E97" s="156"/>
+    </row>
+    <row r="98" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E98" s="156"/>
+    </row>
+    <row r="99" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E99" s="156"/>
+    </row>
+    <row r="100" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E100" s="156"/>
+    </row>
+    <row r="101" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E101" s="156"/>
+    </row>
+    <row r="102" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E102" s="156"/>
+    </row>
+    <row r="103" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E103" s="156"/>
+    </row>
+    <row r="104" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E104" s="156"/>
+    </row>
+    <row r="105" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E105" s="156"/>
+    </row>
+    <row r="106" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E106" s="156"/>
+    </row>
+    <row r="107" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E107" s="156"/>
+    </row>
+    <row r="108" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E108" s="156"/>
+    </row>
+    <row r="109" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E109" s="156"/>
+    </row>
+    <row r="110" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E110" s="156"/>
+    </row>
+    <row r="111" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E111" s="156"/>
+    </row>
+    <row r="112" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E112" s="156"/>
+    </row>
+    <row r="113" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E113" s="156"/>
+    </row>
+    <row r="114" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E114" s="156"/>
+    </row>
+    <row r="115" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E115" s="156"/>
+    </row>
+    <row r="116" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E116" s="156"/>
+    </row>
+    <row r="117" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E117" s="156"/>
+    </row>
+    <row r="118" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E118" s="156"/>
+    </row>
+    <row r="119" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E119" s="156"/>
+    </row>
+    <row r="120" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E120" s="156"/>
+    </row>
+    <row r="121" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E121" s="156"/>
+    </row>
+    <row r="122" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E122" s="156"/>
+    </row>
+    <row r="123" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E123" s="156"/>
+    </row>
+    <row r="124" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E124" s="156"/>
+    </row>
+    <row r="125" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E125" s="156"/>
+    </row>
+    <row r="126" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E126" s="156"/>
+    </row>
+    <row r="127" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E127" s="156"/>
+    </row>
+    <row r="128" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E128" s="156"/>
+    </row>
+    <row r="129" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E129" s="156"/>
+    </row>
+    <row r="130" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E130" s="156"/>
+    </row>
+    <row r="131" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E131" s="156"/>
+    </row>
+    <row r="132" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E132" s="156"/>
+    </row>
+    <row r="133" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E133" s="156"/>
+    </row>
+    <row r="134" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E134" s="156"/>
+    </row>
+    <row r="135" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E135" s="156"/>
+    </row>
+    <row r="136" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E136" s="156"/>
+    </row>
+    <row r="137" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E137" s="156"/>
+    </row>
+    <row r="138" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E138" s="156"/>
+    </row>
+    <row r="139" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E139" s="156"/>
+    </row>
+    <row r="140" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E140" s="156"/>
+    </row>
+    <row r="141" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E141" s="156"/>
+    </row>
+    <row r="142" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E142" s="156"/>
+    </row>
+    <row r="143" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E143" s="156"/>
+    </row>
+    <row r="144" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E144" s="156"/>
+    </row>
+    <row r="145" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E145" s="156"/>
+    </row>
+    <row r="146" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E146" s="156"/>
+    </row>
+    <row r="147" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E147" s="156"/>
+    </row>
+    <row r="148" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E148" s="156"/>
+    </row>
+    <row r="149" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E149" s="156"/>
+    </row>
+    <row r="150" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E150" s="156"/>
+    </row>
+    <row r="151" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E151" s="156"/>
+    </row>
+    <row r="152" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E152" s="156"/>
+    </row>
+    <row r="153" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E153" s="156"/>
+    </row>
+    <row r="154" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E154" s="156"/>
+    </row>
+    <row r="155" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E155" s="156"/>
+    </row>
+    <row r="156" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E156" s="156"/>
+    </row>
+    <row r="157" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E157" s="156"/>
+    </row>
+    <row r="158" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E158" s="156"/>
+    </row>
+    <row r="159" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E159" s="156"/>
+    </row>
+    <row r="160" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E160" s="156"/>
+    </row>
+    <row r="161" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E161" s="156"/>
+    </row>
+    <row r="162" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E162" s="156"/>
+    </row>
+    <row r="163" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E163" s="156"/>
+    </row>
+    <row r="164" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E164" s="156"/>
+    </row>
+    <row r="165" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E165" s="156"/>
+    </row>
+    <row r="166" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E166" s="156"/>
+    </row>
+    <row r="167" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E167" s="156"/>
+    </row>
+    <row r="168" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E168" s="156"/>
+    </row>
+    <row r="169" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E169" s="156"/>
+    </row>
+    <row r="170" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E170" s="156"/>
+    </row>
+    <row r="171" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E171" s="156"/>
+    </row>
+    <row r="172" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E172" s="156"/>
+    </row>
+    <row r="173" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E173" s="156"/>
+    </row>
+    <row r="174" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E174" s="156"/>
+    </row>
+    <row r="175" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E175" s="156"/>
+    </row>
+    <row r="176" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E176" s="156"/>
+    </row>
+    <row r="177" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E177" s="156"/>
+    </row>
+    <row r="178" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E178" s="156"/>
+    </row>
+    <row r="179" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E179" s="156"/>
+    </row>
+    <row r="180" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E180" s="156"/>
+    </row>
+    <row r="181" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E181" s="156"/>
+    </row>
+    <row r="182" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E182" s="156"/>
+    </row>
+    <row r="183" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E183" s="156"/>
+    </row>
+    <row r="184" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E184" s="156"/>
+    </row>
+    <row r="185" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E185" s="156"/>
+    </row>
+    <row r="186" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E186" s="156"/>
+    </row>
+    <row r="187" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E187" s="156"/>
+    </row>
+    <row r="188" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E188" s="156"/>
+    </row>
+    <row r="189" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E189" s="156"/>
+    </row>
+    <row r="190" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E190" s="156"/>
+    </row>
+    <row r="191" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E191" s="156"/>
+    </row>
+    <row r="192" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E192" s="156"/>
+    </row>
+    <row r="193" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E193" s="156"/>
+    </row>
+    <row r="194" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E194" s="156"/>
+    </row>
+    <row r="195" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E195" s="156"/>
+    </row>
+    <row r="196" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E196" s="156"/>
+    </row>
+    <row r="197" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E197" s="156"/>
+    </row>
+    <row r="198" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E198" s="156"/>
+    </row>
+    <row r="199" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E199" s="156"/>
+    </row>
+    <row r="200" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E200" s="156"/>
+    </row>
+    <row r="201" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E201" s="156"/>
+    </row>
+    <row r="202" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E202" s="156"/>
+    </row>
+    <row r="203" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E203" s="156"/>
+    </row>
+    <row r="204" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E204" s="156"/>
+    </row>
+    <row r="205" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E205" s="156"/>
+    </row>
+    <row r="206" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E206" s="156"/>
+    </row>
+    <row r="207" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E207" s="156"/>
+    </row>
+    <row r="208" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E208" s="156"/>
+    </row>
+    <row r="209" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E209" s="156"/>
+    </row>
+    <row r="210" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E210" s="156"/>
+    </row>
+    <row r="211" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E211" s="156"/>
+    </row>
+    <row r="212" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E212" s="156"/>
+    </row>
+    <row r="213" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E213" s="156"/>
+    </row>
+    <row r="214" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E214" s="156"/>
+    </row>
+    <row r="215" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E215" s="156"/>
+    </row>
+    <row r="216" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E216" s="156"/>
+    </row>
+    <row r="217" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E217" s="156"/>
+    </row>
+    <row r="218" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E218" s="156"/>
+    </row>
+    <row r="219" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E219" s="156"/>
+    </row>
+    <row r="220" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E220" s="156"/>
+    </row>
+    <row r="221" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E221" s="156"/>
+    </row>
+    <row r="222" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E222" s="156"/>
+    </row>
+    <row r="223" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E223" s="156"/>
+    </row>
+    <row r="224" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E224" s="156"/>
+    </row>
+    <row r="225" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E225" s="156"/>
+    </row>
+    <row r="226" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E226" s="156"/>
+    </row>
+    <row r="227" spans="5:5" ht="15.75" customHeight="1">
+      <c r="E227" s="156"/>
+    </row>
+    <row r="228" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="229" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="230" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="231" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="232" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="233" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="234" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="235" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="236" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="237" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="238" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="239" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="240" spans="5:5" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7A6E799-3425-7049-AD78-3DEC34B23389}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15.75" customHeight="1"/>
@@ -10227,7 +14600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B4CD89-6261-8048-A311-C06279C67C7B}">
   <dimension ref="A1:U1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="111" customHeight="1"/>
@@ -10262,7 +14635,7 @@
       <c r="A2" s="72" t="s">
         <v>1261</v>
       </c>
-      <c r="B2" s="77">
+      <c r="B2" s="138">
         <v>1</v>
       </c>
       <c r="C2" s="128" t="s">
@@ -10275,7 +14648,7 @@
         <v>1274</v>
       </c>
       <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
+      <c r="G2" s="139"/>
       <c r="H2" s="78"/>
       <c r="I2" s="78"/>
       <c r="J2" s="78"/>
@@ -10295,7 +14668,7 @@
       <c r="A3" s="72" t="s">
         <v>1261</v>
       </c>
-      <c r="B3" s="77">
+      <c r="B3" s="138">
         <v>2</v>
       </c>
       <c r="C3" s="128" t="s">
@@ -10312,7 +14685,7 @@
       <c r="A4" s="72" t="s">
         <v>1261</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="138">
         <v>3</v>
       </c>
       <c r="C4" s="128" t="s">
@@ -10329,7 +14702,7 @@
       <c r="A5" s="72" t="s">
         <v>1261</v>
       </c>
-      <c r="B5" s="75">
+      <c r="B5" s="138">
         <v>4</v>
       </c>
       <c r="C5" s="73" t="s">
@@ -10346,7 +14719,7 @@
       <c r="A6" s="72" t="s">
         <v>1261</v>
       </c>
-      <c r="B6" s="75">
+      <c r="B6" s="138">
         <v>5</v>
       </c>
       <c r="C6" s="128" t="s">
@@ -10363,7 +14736,7 @@
       <c r="A7" s="72" t="s">
         <v>1261</v>
       </c>
-      <c r="B7" s="75">
+      <c r="B7" s="138">
         <v>6</v>
       </c>
       <c r="C7" s="73" t="s">
@@ -10380,7 +14753,7 @@
       <c r="A8" s="72" t="s">
         <v>1251</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="138">
         <v>7</v>
       </c>
       <c r="C8" s="73" t="s">
@@ -10397,7 +14770,7 @@
       <c r="A9" s="72" t="s">
         <v>1251</v>
       </c>
-      <c r="B9" s="75">
+      <c r="B9" s="138">
         <v>8</v>
       </c>
       <c r="C9" s="73" t="s">
@@ -10414,7 +14787,7 @@
       <c r="A10" s="72" t="s">
         <v>1251</v>
       </c>
-      <c r="B10" s="75">
+      <c r="B10" s="138">
         <v>9</v>
       </c>
       <c r="C10" s="73" t="s">
@@ -10431,7 +14804,7 @@
       <c r="A11" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="138">
         <v>10</v>
       </c>
       <c r="C11" s="74" t="s">
@@ -10448,7 +14821,7 @@
       <c r="A12" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B12" s="75">
+      <c r="B12" s="138">
         <v>11</v>
       </c>
       <c r="C12" s="74" t="s">
@@ -10465,7 +14838,7 @@
       <c r="A13" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B13" s="75">
+      <c r="B13" s="138">
         <v>12</v>
       </c>
       <c r="C13" s="73" t="s">
@@ -10482,7 +14855,7 @@
       <c r="A14" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="138">
         <v>13</v>
       </c>
       <c r="C14" s="73" t="s">
@@ -10499,7 +14872,7 @@
       <c r="A15" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B15" s="75">
+      <c r="B15" s="138">
         <v>14</v>
       </c>
       <c r="C15" s="73" t="s">
@@ -10516,7 +14889,7 @@
       <c r="A16" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B16" s="75">
+      <c r="B16" s="138">
         <v>15</v>
       </c>
       <c r="C16" s="73" t="s">
@@ -10533,7 +14906,7 @@
       <c r="A17" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B17" s="75">
+      <c r="B17" s="138">
         <v>16</v>
       </c>
       <c r="C17" s="74" t="s">
@@ -10550,7 +14923,7 @@
       <c r="A18" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B18" s="75">
+      <c r="B18" s="138">
         <v>17</v>
       </c>
       <c r="C18" s="73" t="s">
@@ -10567,7 +14940,7 @@
       <c r="A19" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B19" s="75">
+      <c r="B19" s="138">
         <v>18</v>
       </c>
       <c r="C19" s="73" t="s">
@@ -10584,7 +14957,7 @@
       <c r="A20" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B20" s="75">
+      <c r="B20" s="138">
         <v>19</v>
       </c>
       <c r="C20" s="74" t="s">
@@ -10601,7 +14974,7 @@
       <c r="A21" s="72" t="s">
         <v>1217</v>
       </c>
-      <c r="B21" s="75">
+      <c r="B21" s="138">
         <v>20</v>
       </c>
       <c r="C21" s="73" t="s">
@@ -10618,7 +14991,7 @@
       <c r="A22" s="72" t="s">
         <v>1207</v>
       </c>
-      <c r="B22" s="75">
+      <c r="B22" s="138">
         <v>21</v>
       </c>
       <c r="C22" s="73" t="s">
@@ -10635,7 +15008,7 @@
       <c r="A23" s="72" t="s">
         <v>1207</v>
       </c>
-      <c r="B23" s="75">
+      <c r="B23" s="138">
         <v>22</v>
       </c>
       <c r="C23" s="73" t="s">
@@ -10652,7 +15025,7 @@
       <c r="A24" s="72" t="s">
         <v>1207</v>
       </c>
-      <c r="B24" s="75">
+      <c r="B24" s="138">
         <v>23</v>
       </c>
       <c r="C24" s="74" t="s">
@@ -10669,7 +15042,7 @@
       <c r="A25" s="72" t="s">
         <v>1197</v>
       </c>
-      <c r="B25" s="75">
+      <c r="B25" s="138">
         <v>24</v>
       </c>
       <c r="C25" s="74" t="s">
@@ -10686,7 +15059,7 @@
       <c r="A26" s="72" t="s">
         <v>1197</v>
       </c>
-      <c r="B26" s="75">
+      <c r="B26" s="138">
         <v>25</v>
       </c>
       <c r="C26" s="73" t="s">
@@ -10703,7 +15076,7 @@
       <c r="A27" s="72" t="s">
         <v>1197</v>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="138">
         <v>26</v>
       </c>
       <c r="C27" s="126" t="s">
@@ -13641,7 +18014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5344526-0759-5748-9599-6774FD0E2E70}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
@@ -14120,7 +18493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD20F301-A307-714C-9879-0F7D8927DA0D}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
@@ -14598,9 +18971,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0227B8-6517-D949-81F0-BC1F8DC37DAA}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="5" customWidth="1"/>
@@ -14609,7 +18982,7 @@
     <col min="4" max="4" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21">
+    <row r="1" spans="1:15" ht="21">
       <c r="A1" s="6" t="s">
         <v>160</v>
       </c>
@@ -14649,8 +19022,14 @@
       <c r="M1" t="s">
         <v>1059</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="119" customHeight="1">
+      <c r="N1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="119" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>159</v>
       </c>
@@ -14690,8 +19069,14 @@
       <c r="M2" s="23" t="s">
         <v>1372</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="159" customHeight="1">
+      <c r="N2" s="173" t="s">
+        <v>1660</v>
+      </c>
+      <c r="O2" s="174" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="159" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>161</v>
       </c>
@@ -14731,8 +19116,14 @@
       <c r="M3" s="23" t="s">
         <v>1373</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="125" customHeight="1">
+      <c r="N3" s="173" t="s">
+        <v>1661</v>
+      </c>
+      <c r="O3" s="175" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="125" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>162</v>
       </c>
@@ -14772,8 +19163,14 @@
       <c r="M4" s="23" t="s">
         <v>1374</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="88" customHeight="1">
+      <c r="N4" s="173" t="s">
+        <v>1662</v>
+      </c>
+      <c r="O4" s="174" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="88" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>163</v>
       </c>
@@ -14813,8 +19210,14 @@
       <c r="M5" s="23" t="s">
         <v>1375</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="128" customHeight="1">
+      <c r="N5" s="173" t="s">
+        <v>1663</v>
+      </c>
+      <c r="O5" s="174" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="128" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>164</v>
       </c>
@@ -14853,6 +19256,12 @@
       </c>
       <c r="M6" s="23" t="s">
         <v>1376</v>
+      </c>
+      <c r="N6" s="173" t="s">
+        <v>1664</v>
+      </c>
+      <c r="O6" s="175" t="s">
+        <v>1680</v>
       </c>
     </row>
   </sheetData>
@@ -14860,9 +19269,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D128F0C-3C92-B24F-9D24-BF419F807E89}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
@@ -15865,6 +20274,142 @@
       </c>
       <c r="G44" s="46" t="s">
         <v>1385</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B45" s="49" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C45" s="49" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D45" s="49" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E45" s="46" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F45" s="49" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G45" s="46" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D46" s="49" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>1674</v>
+      </c>
+      <c r="G46" s="46" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B47" s="176" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C47" s="176" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D47" s="176" t="s">
+        <v>428</v>
+      </c>
+      <c r="E47" s="177" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F47" s="176" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G47" s="178" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B48" s="179" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C48" s="179" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D48" s="179" t="s">
+        <v>428</v>
+      </c>
+      <c r="E48" s="180" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F48" s="179" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G48" s="180" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B49" s="49" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>1694</v>
+      </c>
+      <c r="G49" s="80" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B50" s="181" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C50" s="181" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D50" s="181" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E50" s="182" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F50" s="181" t="s">
+        <v>1700</v>
+      </c>
+      <c r="G50" s="181" t="s">
+        <v>1701</v>
       </c>
     </row>
   </sheetData>
@@ -15912,14 +20457,17 @@
     <hyperlink ref="E42" r:id="rId41" xr:uid="{48E273F6-ED98-9A4D-B926-3360708B7FC2}"/>
     <hyperlink ref="E43" r:id="rId42" xr:uid="{AF1B887C-35B7-8E4D-91D8-29E3CA5ACE86}"/>
     <hyperlink ref="E44" r:id="rId43" xr:uid="{D9F36DA3-D0B7-7E42-85A4-528353BCA0E2}"/>
+    <hyperlink ref="E45" r:id="rId44" xr:uid="{8E9A5898-D760-C34B-BCAE-3253D0395A4E}"/>
+    <hyperlink ref="E46" r:id="rId45" xr:uid="{24343D11-14C1-314D-A150-F004F302B6B0}"/>
+    <hyperlink ref="E47" r:id="rId46" xr:uid="{7FF3B79D-3400-6643-92FC-186734B7FF70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C35D0C-FC96-9247-B6ED-A62B9AB8F511}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -16168,6 +20716,46 @@
       </c>
       <c r="F12" t="s">
         <v>1064</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="108" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="108" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1654</v>
       </c>
     </row>
   </sheetData>

--- a/assets/LadenburgConsensuStatements.xlsx
+++ b/assets/LadenburgConsensuStatements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E5AD0F-1B36-6349-954F-A503A8893933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74CAFAF-A810-2149-AEEA-900A67078305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12400" yWindow="620" windowWidth="35980" windowHeight="21980" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12400" yWindow="620" windowWidth="35980" windowHeight="21980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="4" r:id="rId1"/>
@@ -21972,7 +21972,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="102">
+    <row r="15" spans="1:6" ht="85">
       <c r="A15" s="23" t="s">
         <v>361</v>
       </c>

--- a/assets/LadenburgConsensuStatements.xlsx
+++ b/assets/LadenburgConsensuStatements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74CAFAF-A810-2149-AEEA-900A67078305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E2A878-286D-0F4C-A28D-EBB2017E4344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12400" yWindow="620" windowWidth="35980" windowHeight="21980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21380" yWindow="2980" windowWidth="35980" windowHeight="21980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="4" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="1702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="1704">
   <si>
     <t>Number</t>
   </si>
@@ -8986,6 +8986,12 @@
   </si>
   <si>
     <t>0009-0006-2622-3642</t>
+  </si>
+  <si>
+    <t>Enunciado Simplificado</t>
+  </si>
+  <si>
+    <t>Informação Contextual</t>
   </si>
 </sst>
 </file>
@@ -21742,10 +21748,10 @@
         <v>1015</v>
       </c>
       <c r="D1" t="s">
-        <v>1016</v>
+        <v>1702</v>
       </c>
       <c r="E1" t="s">
-        <v>1017</v>
+        <v>1703</v>
       </c>
       <c r="F1" s="108" t="s">
         <v>1471</v>
@@ -21972,7 +21978,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="85">
+    <row r="15" spans="1:6" ht="102">
       <c r="A15" s="23" t="s">
         <v>361</v>
       </c>
@@ -21989,7 +21995,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="51">
+    <row r="16" spans="1:6" ht="68">
       <c r="A16" s="23" t="s">
         <v>361</v>
       </c>

--- a/assets/LadenburgConsensuStatements.xlsx
+++ b/assets/LadenburgConsensuStatements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E2A878-286D-0F4C-A28D-EBB2017E4344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AAB4E8-C6EA-6D4D-9EFE-A690A9848BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21380" yWindow="2980" windowWidth="35980" windowHeight="21980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9320" yWindow="3260" windowWidth="35980" windowHeight="21980" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="4" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="1704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="1719">
   <si>
     <t>Number</t>
   </si>
@@ -8993,6 +8993,51 @@
   <si>
     <t>Informação Contextual</t>
   </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>Tópicos Importantes</t>
+  </si>
+  <si>
+    <t>Ana mesajlar</t>
+  </si>
+  <si>
+    <t>Kluczowe wiadomości</t>
+  </si>
+  <si>
+    <t>Messaggi chiave</t>
+  </si>
+  <si>
+    <t>关键信息</t>
+  </si>
+  <si>
+    <t>Messages clés</t>
+  </si>
+  <si>
+    <t>پیام‌های کلیدی</t>
+  </si>
+  <si>
+    <t>Belangrijkste boodschappen</t>
+  </si>
+  <si>
+    <t>Nøglebudskaber</t>
+  </si>
+  <si>
+    <t>Klíčová sdělení</t>
+  </si>
+  <si>
+    <t>Mensajes clave</t>
+  </si>
+  <si>
+    <t>重要なメッセージ</t>
+  </si>
+  <si>
+    <t>Kernbotschaften</t>
+  </si>
+  <si>
+    <t>핵심 메시지 </t>
+  </si>
 </sst>
 </file>
 
@@ -9001,7 +9046,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-3000401]0"/>
   </numFmts>
-  <fonts count="114">
+  <fonts count="115">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -9775,6 +9820,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -10398,7 +10449,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -10868,6 +10919,7 @@
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="46">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -18979,7 +19031,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0227B8-6517-D949-81F0-BC1F8DC37DAA}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="5" customWidth="1"/>
@@ -19035,240 +19087,330 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="119" customHeight="1">
+    <row r="2" spans="1:15" ht="21">
       <c r="A2" s="6" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D2" s="183" t="s">
+        <v>1705</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1716</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="119" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C3" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D3" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E3" s="64" t="s">
         <v>677</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F3" s="66" t="s">
         <v>682</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G3" s="79" t="s">
         <v>770</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H3" s="23" t="s">
         <v>817</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I3" s="107" t="s">
         <v>988</v>
       </c>
-      <c r="J2" s="111" t="s">
+      <c r="J3" s="111" t="s">
         <v>1095</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K3" s="72" t="s">
         <v>1178</v>
       </c>
-      <c r="L2" s="132" t="s">
+      <c r="L3" s="132" t="s">
         <v>1287</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M3" s="23" t="s">
         <v>1372</v>
       </c>
-      <c r="N2" s="173" t="s">
+      <c r="N3" s="173" t="s">
         <v>1660</v>
       </c>
-      <c r="O2" s="174" t="s">
+      <c r="O3" s="174" t="s">
         <v>1676</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="159" customHeight="1">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:15" ht="159" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="E3" s="65" t="s">
+      <c r="E4" s="65" t="s">
         <v>678</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F4" s="67" t="s">
         <v>683</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G4" s="79" t="s">
         <v>771</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H4" s="23" t="s">
         <v>818</v>
       </c>
-      <c r="I3" s="107" t="s">
+      <c r="I4" s="107" t="s">
         <v>989</v>
       </c>
-      <c r="J3" s="111" t="s">
+      <c r="J4" s="111" t="s">
         <v>1096</v>
       </c>
-      <c r="K3" s="72" t="s">
+      <c r="K4" s="72" t="s">
         <v>1179</v>
       </c>
-      <c r="L3" s="132" t="s">
+      <c r="L4" s="132" t="s">
         <v>1288</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M4" s="23" t="s">
         <v>1373</v>
       </c>
-      <c r="N3" s="173" t="s">
+      <c r="N4" s="173" t="s">
         <v>1661</v>
       </c>
-      <c r="O3" s="175" t="s">
+      <c r="O4" s="175" t="s">
         <v>1677</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="125" customHeight="1">
-      <c r="A4" s="6" t="s">
+    <row r="5" spans="1:15" ht="125" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C5" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D5" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E5" s="65" t="s">
         <v>679</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F5" s="68" t="s">
         <v>684</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G5" s="79" t="s">
         <v>772</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H5" s="23" t="s">
         <v>819</v>
       </c>
-      <c r="I4" s="107" t="s">
+      <c r="I5" s="107" t="s">
         <v>990</v>
       </c>
-      <c r="J4" s="111" t="s">
+      <c r="J5" s="111" t="s">
         <v>1097</v>
       </c>
-      <c r="K4" s="72" t="s">
+      <c r="K5" s="72" t="s">
         <v>1180</v>
       </c>
-      <c r="L4" s="132" t="s">
+      <c r="L5" s="132" t="s">
         <v>1289</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M5" s="23" t="s">
         <v>1374</v>
       </c>
-      <c r="N4" s="173" t="s">
+      <c r="N5" s="173" t="s">
         <v>1662</v>
       </c>
-      <c r="O4" s="174" t="s">
+      <c r="O5" s="174" t="s">
         <v>1678</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="88" customHeight="1">
-      <c r="A5" s="6" t="s">
+    <row r="6" spans="1:15" ht="88" customHeight="1">
+      <c r="A6" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C6" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="E5" s="65" t="s">
+      <c r="E6" s="65" t="s">
         <v>680</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F6" s="68" t="s">
         <v>685</v>
       </c>
-      <c r="G5" s="79" t="s">
+      <c r="G6" s="79" t="s">
         <v>773</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H6" s="23" t="s">
         <v>820</v>
       </c>
-      <c r="I5" s="107" t="s">
+      <c r="I6" s="107" t="s">
         <v>991</v>
       </c>
-      <c r="J5" s="111" t="s">
+      <c r="J6" s="111" t="s">
         <v>1098</v>
       </c>
-      <c r="K5" s="72" t="s">
+      <c r="K6" s="72" t="s">
         <v>1181</v>
       </c>
-      <c r="L5" s="132" t="s">
+      <c r="L6" s="132" t="s">
         <v>1290</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M6" s="23" t="s">
         <v>1375</v>
       </c>
-      <c r="N5" s="173" t="s">
+      <c r="N6" s="173" t="s">
         <v>1663</v>
       </c>
-      <c r="O5" s="174" t="s">
+      <c r="O6" s="174" t="s">
         <v>1679</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="128" customHeight="1">
-      <c r="A6" s="6" t="s">
+    <row r="7" spans="1:15" ht="128" customHeight="1">
+      <c r="A7" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D7" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="E6" s="65" t="s">
+      <c r="E7" s="65" t="s">
         <v>681</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F7" s="68" t="s">
         <v>686</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G7" s="79" t="s">
         <v>774</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H7" s="23" t="s">
         <v>821</v>
       </c>
-      <c r="I6" s="107" t="s">
+      <c r="I7" s="107" t="s">
         <v>992</v>
       </c>
-      <c r="J6" s="111" t="s">
+      <c r="J7" s="111" t="s">
         <v>1099</v>
       </c>
-      <c r="K6" s="72" t="s">
+      <c r="K7" s="72" t="s">
         <v>1182</v>
       </c>
-      <c r="L6" s="132" t="s">
+      <c r="L7" s="132" t="s">
         <v>1291</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M7" s="23" t="s">
         <v>1376</v>
       </c>
-      <c r="N6" s="173" t="s">
+      <c r="N7" s="173" t="s">
         <v>1664</v>
       </c>
-      <c r="O6" s="175" t="s">
+      <c r="O7" s="175" t="s">
         <v>1680</v>
       </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="C10" s="183"/>
+      <c r="D10" s="183"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="C13" s="108"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="C14" s="108"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="C15" s="108"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="C16" s="108"/>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="108"/>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="108"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="108"/>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="108"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="108"/>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="108"/>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="108"/>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="108"/>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="108"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -21995,7 +22137,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="68">
+    <row r="16" spans="1:6" ht="51">
       <c r="A16" s="23" t="s">
         <v>361</v>
       </c>
